--- a/results/qwen3_5_9b/comparison_CoTPlainLLM/CoTPlainLLM_results.xlsx
+++ b/results/qwen3_5_9b/comparison_CoTPlainLLM/CoTPlainLLM_results.xlsx
@@ -723,7 +723,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Adamax Optimizer implementation.
+Adamax is an optimization algorithm that uses the infinity norm for normalization,
+making it robust to features with different scales. It is a variant of Adam that
+uses max() instead of square root in the denominator.
+    Attributes:
+            Default is 1e-07.
+    Args:
+            or callable that returns a float/tensor.
+    Returns:
+    Raises:
+    Examples:
+        &gt;&gt;&gt; optimizer = Adamax(learning_rate=0.001, beta_1=0.9, beta_2=0.999)
+        &gt;&gt;&gt; optimizer.minimize(loss_fn, var_list=[model_variables])
+    Note:
+        estimates and 'v' for second moment estimates using infinity norm normalization.
+        Suitable for training deep neural networks with sparse or dense gradients.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -840,7 +855,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Transform samples based on label groupings for agglomerative clustering.
+This transformer aggregates input data according to sample labels using a specified
+pooling function (e.g., mean, median). It is designed to work with hierarchical
+clustering where samples are grouped by their cluster assignments.
+Parameters
+----------
+    Input data to transform. Each row represents a sample.
+Returns
+-------
+    Transformed/aggregated data based on label groupings. Shape depends on
+    the pooling function and whether mean pooling is used with non-sparse data.
+Raises
+------
+NotFittedError
+    If the transformer has not been fitted before calling transform().
+ValueError
+    If input data is invalid or incompatible with the configured parameters.
+Notes
+-----
+- When pooling_func is np.mean and X is not sparse, aggregation uses bincount
+- For other pooling functions or sparse data, samples are grouped by unique
+  labels and the pooling function is applied to each group.
+- The inverse_transform method reconstructs the original structure using label
+  inverse mapping (deprecated Xt parameter handling included).
+Examples
+--------
+&gt;&gt;&gt; from sklearn.cluster import AgglomerativeClustering
+&gt;&gt;&gt; from sklearn.preprocessing import AgglomerationTransform
+&gt;&gt;&gt; # Fit clustering model
+&gt;&gt;&gt; clusterer = AgglomerativeClustering(n_clusters=3)
+&gt;&gt;&gt; X = np.random.rand(100, 2)
+&gt;&gt;&gt; labels = clusterer.fit_predict(X)
+&gt;&gt;&gt; # Transform using mean pooling
+&gt;&gt;&gt; transform = AgglomerationTransform(labels_, labels, pooling_func=np.mean)
+&gt;&gt;&gt; transform.transform(X)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -1052,7 +1101,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D Average Pooling Layer.
+Applies average pooling over the input data using a specified window size.
+This layer reduces spatial dimensions by computing the average value over
+the pooling region.
+Args:
+        pooling window. If an integer is provided, it will be applied to
+        both dimensions. Default is 2.
+        the pooling operation. If None, defaults to pool_size. Default is None.
+        before applying the pooling operation. 'valid' applies no padding,
+        Default is 'valid'.
+        or 'channels_first'. Determines whether channel dimension comes last
+        or first in the tensor.
+Returns:
+    None. This is a layer constructor that returns self.
+Raises:
+Example:
+    &gt;&gt;&gt; from tensorflow.keras.layers import AveragePooling1D
+    &gt;&gt;&gt; avg_pool = AveragePooling1D(pool_size=2, strides=1)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1264,7 +1330,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Applies average pooling over a volume of size (batch_size, channels, height, width) or similar depending on data_format.
+Args:
+Returns:
+    None (initializes the layer).
+Raises:</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1400,7 +1470,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>3D Average Pooling Layer.
+This layer applies average pooling over a 3D input volume by computing the mean value
+over each region of size pool_size in the height, width, and depth dimensions. It is
+commonly used to downscale feature maps while retaining spatial information in
+convolutional neural networks.
+Args:
+        each dimension (height, width, depth). Default is (2, 2, 2).
+        dimension. If None, defaults to pool_size. Default is None.
+        or 'same' (padded to maintain spatial dimensions). Default is 'valid'.
+        'channels_last' (default for most Keras models) or 'channels_first'.
+        Default is None, which inherits from parent class.
+Returns:
+    None
+Raises:
+Examples:
+    &gt;&gt;&gt; layer = AveragePooling3D(pool_size=(2, 2, 2), strides=(1, 1, 1))
+    &gt;&gt;&gt; layer = AveragePooling3D(pool_size=(3, 3, 3), padding='same')</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2393,7 +2479,84 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Bayesian Gaussian Mixture Model.
+This class implements a Bayesian Gaussian Mixture Model using prior distributions
+mixture model with additional Bayesian priors to prevent overfitting and handle
+cases with few samples or high-dimensional data.
+The model uses an Expectation-Maximization (EM) algorithm with Bayesian updates
+- Mixture weights (Dirichlet process or Dirichlet distribution)
+- Component means (normal prior)
+- Precision matrices (Wishart prior)
+- Covariance matrices (Wishart prior)
+This provides regularization and helps avoid convergence to poor local optima.
+The model is particularly useful when the number of samples is small relative
+to the number of features, or when prior knowledge about the data distribution
+is available.
+Parameters
+----------
+    Number of mixture components in the model. Must be at least 2 for a
+    meaningful mixture.
+    Type of covariance matrix to use for each component. Options are:
+      parameters per component)
+    Convergence tolerance for the EM algorithm. The algorithm stops when the
+    log-likelihood improvement is less than this value between iterations.
+    Regularization constant added to the covariance matrix diagonal to ensure
+    numerical stability and prevent singularity issues during inversion.
+    Maximum number of iterations for the EM algorithm before termination.
+    Number of initializations with different random seeds. The best model is
+    selected based on log-likelihood across all initializations.
+    Method for initializing component means:
+    Type of prior distribution for mixture weights. Options are:
+    Concentration parameter for the weight prior. If None, defaults to 
+    1/n_components. For dirichlet_process type, this affects the stick-breaking
+    process parameters.
+    Prior precision (inverse variance) for component means. If None, defaults
+    to 1.0. Higher values indicate stronger prior belief about mean locations.
+    Prior mean vector for components with shape (n_features,). If None, 
+    computed as the overall data mean across all samples.
+    Degrees of freedom prior for covariance matrices. Must be greater than
+    n_features - 1. If None, defaults to n_features. Higher values indicate
+    stronger belief in the prior covariance structure.
+    Prior covariance matrix for components. Shape depends on covariance_type:
+    If None, computed from the data using appropriate statistics.
+    Controls random number generation for reproducibility. Used for:
+    - Initial component mean selection
+    - K-means initialization when init_params='kmeans'
+    - Any other stochastic operations in the algorithm
+    If True, reuses results from previous fit() call as initialization.
+    Useful for incremental fitting or fine-tuning after initial convergence.
+    Verbosity level:
+    Interval between verbose output messages when verbose &gt; 0. Messages are
+    printed every verbose_interval iterations.
+Returns
+-------
+None
+    This class is typically used as a mixin or base class. The fit() method
+    (not shown here) returns self for method chaining.
+Raises
+------
+ValueError
+    If degrees_of_freedom_prior is not greater than n_features - 1, or if
+    covariance_prior shape doesn't match the specified covariance_type 
+    requirements.
+See Also
+--------
+Examples
+--------
+&gt;&gt;&gt; from sklearn.mixture import BayesianGaussianMixture
+&gt;&gt;&gt; import numpy as np
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Generate sample data from two Gaussian distributions
+&gt;&gt;&gt; X = np.vstack([np.random.randn(50, 2), np.random.randn(50, 2) + 3])
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Fit a Bayesian GMM with 2 components
+&gt;&gt;&gt; bgm = BayesianGaussianMixture(n_components=2, random_state=42)
+&gt;&gt;&gt; bgm.fit(X)
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Access fitted parameters
+&gt;&gt;&gt; print(bgm.weights_)
+&gt;&gt;&gt; print(bgm.means_)
+&gt;&gt;&gt; print(bgm.covariances_)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2926,7 +3089,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Base class for convolutional layers in Keras.
+This layer performs a convolution operation on input data, supporting
+various spatial dimensions (1D, 2D, or 3D) through the rank parameter.
+It supports grouped convolutions, causal padding, and various activation
+functions.
+Args:
+        convolution operation. Common values are 1, 2, or 3.
+        Can be a float that will be converted to int. Must be positive and
+        evenly divisible by groups.
+        dimension. Default is 1. Cannot contain zero values.
+        'causal'). Causal padding is only supported for Conv1D and
+        SeparableConv1D layers. Default is 'valid'.
+        'channels_last'). Default is None, which uses the global default.
+        spatial dimension. Controls the spacing between kernel elements.
+        Default is 1.
+        channels are split into groups, and each group has its own set of
+        filters. Default is 1 (standard convolution).
+        Can be a string or callable. Set to None for no activation.
+        convolution operation. Default is True.
+        (e.g., 'glorot_uniform') or a Keras initializer object.
+        a Keras initializer object. Default is 'zeros'.
+        a string or a Keras regularizer object.
+        string or a Keras regularizer object.
+        string or a Keras constraint object.
+        string or a Keras constraint object.
+        trainable during model training. Default is True.
+        generated name will be used.
+        default one.
+Returns:
+    None. This is a layer class that should be instantiated and added to a
+    model or used directly for inference.
+Raises:
+        groups, if kernel_size or strides contain zero values, if causal
+        padding is used with unsupported layer types (Conv1D or SeparableConv1D),
+        or if the input channel dimension is undefined.
+Examples:
+    &gt;&gt;&gt; # 2D convolution with 32 filters and 3x3 kernel
+    &gt;&gt;&gt; conv = Conv(rank=2, filters=32, kernel_size=(3, 3), padding='same')
+    &gt;&gt;&gt;
+    &gt;&gt;&gt; # 1D convolution with causal padding
+    &gt;&gt;&gt; conv_1d = Conv(rank=1, filters=64, kernel_size=5, padding='causal')
+    &gt;&gt;&gt;
+    &gt;&gt;&gt; # Grouped convolution with 2 groups
+    &gt;&gt;&gt; grouped_conv = Conv(rank=3, filters=96, kernel_size=(3, 3, 3),
+    ...                     groups=2)
+See Also:
+    Conv1D, Conv2D, Conv3D, SeparableConv1D, SeparableConv2D, SeparableConv3D</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -3142,7 +3351,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>A one-dimensional (1D) convolutional layer.
+This layer applies a set of convolution filters along a single spatial dimension,
+making it suitable for processing 1D signals such as time series or audio data.
+Args:
+        of filters in the convolution).
+        window for each feature map. Can be a single integer to specify the same
+        value for all feature maps.
+        Specifies the type of padding to apply. 'valid' means no padding, 'same'
+        means the output has the same dimension as the input.
+        ordering of the dimensions in the inputs. 'channels_last' corresponds
+        to inputs with shape (batch, steps, filters) and outputs with shape
+        (batch, new_steps, filters). 'channels_first' corresponds to inputs
+        (batch, filters, new_steps). Defaults to 'channels_last'.
+        feature map. When greater than 1, it scales the kernel by inserting
+        zeros between elements.
+        performs standard convolution. When equal to filters, performs depthwise
+        convolution. Defaults to 1.
+        Can be a string (e.g., 'relu', 'sigmoid') or a callable. If None, no
+        activation is applied. The actual function is lazily loaded from
+        the activations registry.
+        convolution operation. Defaults to True.
+        initialization function (e.g., 'glorot_uniform', 'he_normal') or an
+        instance of a custom initializer. Lazily loaded from the initializers
+        registry.
+        Defaults to 'zeros'. Lazily loaded from the initializers registry.
+        regularization to the kernel weights. Defaults to None.
+        regularization to the bias vector. Defaults to None.
+        regularization to the output activation. Defaults to None.
+        the kernel weights. Defaults to None.
+        the bias vector. Defaults to None.
+Returns:
+Raises:
+        unsupported padding type, or incompatible kernel_size).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3538,7 +3779,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D Transposed Convolution Layer (Deconvolution)
+This layer implements a 1D transposed convolution operation, commonly used for
+upsampling in neural networks such as autoencoders and GANs. The layer learns
+a filter that performs the inverse of a standard convolution operation.
+Attributes:
+        Number of output filters (channels) in the convolution.
+        Size of the convolution kernel along the temporal dimension. Can be an
+        integer for uniform size or a tuple/list for different sizes per axis.
+        Stride values for the transposed convolution. Default is 1.
+        Padding type ('valid', 'same', 'causal'). Default is 'valid'.
+        Additional padding added to the output dimension. Must be less than stride.
+        Dilation rate for the kernel. Default is 1.
+        Activation function to apply after the transposed convolution.
+        Whether to include a bias term in the layer. Default is True.
+        Initializer for the kernel weights. Default is 'glorot_uniform'.
+        Initializer for the bias vector. Default is 'zeros'.
+        Regularizer applied to the kernel weights.
+        Regularizer applied to the bias term.
+        Regularizer applied to the layer's output.
+        Constraint applied to the kernel weights.
+        Constraint applied to the bias term.
+Methods:
+Raises:
+                output_padding is greater than or equal to stride values.
+Examples:
+    &gt;&gt;&gt; from tensorflow.keras.layers import Conv1DTranspose
+    &gt;&gt;&gt; conv = Conv1DTranspose(filters=64, kernel_size=3, strides=2)
+    &gt;&gt;&gt; model = tf.keras.Sequential([conv])</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3790,7 +4058,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>2D Convolutional Layer for Neural Networks.
+A convolutional layer that applies a set of learned filters to an input image,
+producing feature maps through the convolution operation. Supports various
+activation functions, padding strategies, and regularization options.
+Args:
+        Must be a positive integer.
+        Can be an integer for square kernels or a tuple for rectangular kernels.
+        Default is (1, 1). Must have two positive integers.
+        to maintain input size). Default is 'valid'.
+        'channels_last'). If None, uses the default from configuration.
+        convolutions. Default is (1, 1). Must have two positive integers.
+        Default is 1 (standard convolution). Must be a positive integer.
+        after convolution. Can be a string name or callable function.
+        Default is None (no activation).
+        Default is True.
+        weights (e.g., 'glorot_uniform', 'he_normal'). Can also be an object.
+        Default is 'glorot_uniform'.
+        values (e.g., 'zeros', 'ones'). Default is 'zeros'.
+        or object to apply to kernel weights. Default is None.
+        or object to apply to bias values. Default is None.
+        or object to apply to layer output. Default is None.
+        or object for kernel weights. Default is None.
+        or object for bias values. Default is None.
+Returns:
+        provided parameters.
+Raises:
+        an integer, kernel_size elements are not integers).
+        'valid' or 'same', groups is not a positive integer, or strides
+        contain non-positive values.
+        are provided that the parent class does not support.
+Examples:
+    &gt;&gt;&gt; layer = Conv2D(filters=32, kernel_size=(3, 3), activation='relu')
+    &gt;&gt;&gt; layer = Conv2D(64, (5, 5), strides=(2, 2), padding='same', use_bias=False)
+    &gt;&gt;&gt; layer = Conv2D(filters=16, kernel_size=3, groups=2, data_format='channels_last')</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -4267,7 +4568,49 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>"""Initialize a Conv2DTranspose layer.
+        Args:
+                Must be less than corresponding stride values. If None, no additional padding is applied.
+        Returns:
+            None. Initializes the layer instance.
+        Raises:
+        Examples:
+            &gt;&gt;&gt; # Basic usage with default parameters
+            &gt;&gt;&gt; layer = Conv2DTranspose(filters=64, kernel_size=(3, 3), strides=(2, 2))
+            &gt;&gt;&gt;
+            &gt;&gt;&gt; # With activation and bias
+            &gt;&gt;&gt; layer = Conv2DTranspose(filters=32, kernel_size=(5, 5),
+            ...                         strides=(2, 2), padding='same',
+            ...                         activation='relu', use_bias=True)
+            &gt;&gt;&gt;
+            &gt;&gt;&gt; # Custom initializer and regularizer
+            &gt;&gt;&gt; layer = Conv2DTranspose(filters=128, kernel_size=(3, 3),
+            ...                         strides=(2, 2), output_padding=(1, 1),
+            ...                         kernel_initializer='he_normal',
+            ...                         kernel_regularizer=l2(0.01))
+        """
+        """Build the layer by creating weight tensors based on input shape.
+        Args:
+                For 2D convolution, should be (height, width, channels) or (channels, height, width).
+        Returns:
+            None. Creates kernel and bias weights if use_bias is True.
+        Raises:
+        """
+        """Apply the transpose convolution operation to input tensors.
+        Args:
+                (batch_size, channels, height, width) depending on data_format.
+        Returns:
+            Output tensor with upsampled spatial dimensions. The output shape is computed
+            based on the deconvolution formula using kernel size, strides, padding, and
+            output_padding parameters.
+        Raises:
+        """
+        """Compute the expected output shape given an input shape.
+        Args:
+        Returns:
+                For a 4D input, returns a 4D shape with upsampled height and width dimensions.
+        Raises:
+        """</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4497,11 +4840,7 @@
         super(Conv3D, self).__init__(rank=3, filters=filters, kernel_size=kernel_size, strides=strides, padding=padding, data_format=data_format, dilation_rate=dilation_rate, groups=groups, activation=activations.get(activation), use_bias=use_bias, kernel_initializer=initializers.get(kernel_initializer), bias_initializer=initializers.get(bias_initializer), kernel_regularizer=regularizers.get(kernel_regularizer), bias_regularizer=regularizers.get(bias_regularizer), activity_regularizer=regularizers.get(activity_regularizer), kernel_constraint=constraints.get(kernel_constraint), bias_constraint=constraints.get(bias_constraint), **kwargs)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -4993,7 +5332,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>3D Transpose Convolution Layer for Upsampling Operations.
+A 3D transpose convolution layer that performs upsampling by reversing the 
+forward pass of a standard 3D convolution. This layer is commonly used in 
+U-Net architectures and other deep learning models requiring spatial 
+upsampling operations.
+Args:
+        filters in the last dimension).
+        the convolution kernel along depth, height, and width axes.
+        Default is (1, 1, 1) which preserves spatial dimensions without 
+        downsampling.
+        'same' ensures the output has the same shape as the input when 
+        stride is 1 and kernel size is odd.
+        to pad along each dimension before convolution. This can be used 
+        to adjust output shape without changing filter count. Must be less 
+        than corresponding stride value for each dimension.
+        determining the order of dimensions in input/output tensors.
+        depth, height, and width axes. Default is (1, 1, 1) for standard 
+        convolution without dilation.
+        is True.
+        'glorot_uniform'.
+        the layer (before activation).
+Returns:
+        Shape is determined by input shape, filters, strides, padding, 
+        and output_padding parameters.
+Raises:
+        corresponding output_padding value.
+        3D convolutions).
+Examples:
+    &gt;&gt;&gt; # Basic usage with default parameters
+    &gt;&gt;&gt; layer = Conv3DTranspose(filters=64, kernel_size=(2, 2, 2), strides=(2, 2, 2))
+    &gt;&gt;&gt; output = layer(input_tensor)
+    &gt;&gt;&gt; # With custom padding and activation
+    &gt;&gt;&gt; layer = Conv3DTranspose(
+    ...     filters=128, 
+    ...     kernel_size=(3, 3, 3), 
+    ...     strides=(2, 2, 2),
+    ...     padding='same',
+    ...     activation='relu'
+    ... )
+    &gt;&gt;&gt; # With output_padding to adjust output shape
+    &gt;&gt;&gt; layer = Conv3DTranspose(
+    ...     filters=64, 
+    ...     kernel_size=(2, 2, 2), 
+    ...     strides=(2, 2, 2),
+    ...     output_padding=(1, 1, 1)
+    ... )
+See Also:</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -5139,7 +5524,30 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D Cropping Layer for Keras/TensorFlow.
+This layer crops 1D inputs along the time dimension by removing a specified
+number of samples from both the left and right sides. It is commonly used to
+remove padding added during convolution operations or to trim sequences before
+processing.
+Args:
+        The first element is the number of samples to remove from the left,
+        and the second element is the number of samples to remove from the right.
+Returns:
+        the sum of left and right crop values. Returns None for dynamic dimensions.
+Raises:
+Examples:
+    &gt;&gt;&gt; # Create a layer that crops 2 samples from each side
+    &gt;&gt;&gt; crop_layer = Cropping1D(cropping=(2, 2))
+    &gt;&gt;&gt; 
+    &gt;&gt;&gt; # Use in a model
+    &gt;&gt;&gt; model = Sequential([
+    ...     Conv1D(32, kernel_size=3),
+    ...     Cropping1D(cropping=(1, 1)),
+    ...     MaxPooling1D(pool_size=2)
+    ... ])
+See Also:
+    - Convolutional layers that add padding (Conv1D, SeparableConv1D)
+    - Padding layer for the opposite operation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -5378,7 +5786,91 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Cropping2D layer for cropping 4D input tensors along height and width dimensions.
+This layer crops images in both vertical (height) and horizontal (width) directions,
+supporting symmetric cropping (equal crop from all sides of an axis) or asymmetric
+cropping (different crop amounts from top/bottom or left/right). It works with
+both 'channels_first' and 'channels_last' data formats.
+Parameters
+----------
+    The amount to crop from the input tensor. Can be specified as:
+    - An integer for symmetric cropping (same crop from all sides)
+    Examples:
+    A string, one of 'channels_first' or 'channels_last'. Defaults to the
+    application-wide default. If None, uses the global default data format.
+Returns
+-------
+None
+    This is a layer class that must be instantiated and used within a model.
+Raises
+------
+ValueError
+    If `cropping` does not have exactly 2 elements (for tuple formats) or
+"""
+__init__(self, cropping=((0, 0), (0, 0)), data_format=None, **kwargs):
+    """Initialize the Cropping2D layer with cropping parameters.
+    Parameters
+    ----------
+        The amount to crop from the input tensor (see class docstring for formats).
+        A string, one of 'channels_first' or 'channels_last'. Defaults to global default.
+    **kwargs
+        Additional keyword arguments passed to the parent Layer constructor.
+    Returns
+    -------
+    None
+        This is a layer class that must be instantiated and used within a model.
+    Raises
+    ------
+    ValueError
+        If `cropping` does not have exactly 2 elements (for tuple formats) or
+    """
+    super(Cropping2D, self).__init__(**kwargs)
+    elif hasattr(cropping, '__len__'):
+        height_cropping = conv_utils.normalize_tuple(cropping[0], 2, '1st entry of cropping')
+        width_cropping = conv_utils.normalize_tuple(cropping[1], 2, '2nd entry of cropping')
+    else:
+"""Compute the output shape after cropping.
+    Parameters
+    ----------
+        The input tensor shape as a tuple/list, e.g., (batch_size, height, width, channels)
+    Returns
+    -------
+    TensorShape
+        A TensorShape object representing the cropped output tensor dimensions.
+        The batch dimension and channel dimension are preserved; height and width
+        are reduced by the cropping amounts from each side.
+    Raises
+    ------
+    None
+    """
+    input_shape = tensor_shape.TensorShape(input_shape).as_list()
+    else:
+"""Apply cropping operation to the input tensor.
+    Parameters
+    ----------
+        The input tensor to crop. Shape depends on `data_format`:
+    Returns
+    -------
+    Tensor
+        The cropped input tensor with reduced height and/or width dimensions.
+    Raises
+    ------
+    None
+    """
+        elif self.cropping[0][1] == 0:
+        elif self.cropping[1][1] == 0:
+    else:
+        elif self.cropping[0][1] == 0:
+        elif self.cropping[1][1] == 0:
+"""Get the configuration dictionary for serializing the layer.
+    Returns
+    -------
+    dict
+        A dictionary containing:
+        - Additional attributes from the parent Layer class
+    Raises
+    ------
+    None</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -5744,7 +6236,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Applies 3D spatial cropping to input tensors, supporting both symmetric and asymmetric cropping across depth, height, and width dimensions.
+This layer crops inputs along their spatial dimensions (excluding the channel dimension) by removing specified amounts from left/right, top/bottom, and front/back of the volume. Supports both 'channels_first' and 'channels_last' data formats with full control over asymmetric cropping per dimension.
+Args:
+Returns:
+Raises:
+Examples:
+    &gt;&gt;&gt; # Symmetric cropping (crop 1 pixel from all sides)
+    &gt;&gt;&gt; layer = Cropping3D(cropping=1)
+    &gt;&gt;&gt;
+    &gt;&gt;&gt; # Asymmetric cropping (different crop amounts per dimension)
+    &gt;&gt;&gt; layer = Cropping3D(cropping=((2, 0), (1, 1), (1, 1)))
+    &gt;&gt;&gt;
+    &gt;&gt;&gt; # Channels last format
+    &gt;&gt;&gt; layer = Cropping3D(cropping=(1, 1), data_format='channels_last')
+See Also:</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -6170,7 +6676,75 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>DBSCAN clustering algorithm implementation.
+Density-Based Spatial Clustering of Applications with Noise (DBSCAN) is a
+clustering algorithm that groups data points based on their density in n-dimensional space.
+It can identify clusters of arbitrary shape and automatically determine the number of
+clusters without requiring it as input. Points that are not near enough to any other
+point are marked as noise (label = -1).
+Attributes:
+        The maximum distance between two samples for them to be considered as in the same
+        neighborhood. Increasing this value will merge more clusters and potentially
+        reduce noise points.
+        The minimum number of samples required to be at a distance of 'eps' from each
+        other to form a core sample. A sample is a core sample if at least 'min_samples'
+        (including itself) are within the neighborhood.
+        The metric to use when calculating distance between instances in a feature array.
+        Possible values for 'metric' include:
+        Alternatively, a callable that accepts two arrays and returns a distance value.
+        Additional keyword arguments for the metric function. Only used when metric is
+        callable or certain string options like 'minkowski'.
+        Algorithm choice for constructing the nearest neighbor search structure:
+        Leaf size for BallTree or KDTree algorithms. Larger values may speed up
+        construction but can affect query performance.
+        Power parameter for the Minkowski metric. If p = 1, this is equivalent to
+        Manhattan distance; if p = 2, it is Euclidean distance. Only used when
+        metric='minkowski'.
+        The number of parallel jobs to run for nearest neighbor searches. If None,
+        then only one job is used. -1 means using all processors.
+Attributes (set after fit):
+        Indices of core samples identified during clustering.
+        Cluster labels for each sample in the input data. Negative values (-1) indicate
+        noise points that are not assigned to any cluster.
+        The centroid of clusters if core samples exist, otherwise an empty array with
+        shape (0, n_features).
+Methods:
+    fit(X, y=None, sample_weight=None)
+        Fit the DBSCAN model to data X and return self.
+        Parameters:
+                Training input samples of shape [n_samples, n_features]. Can be a
+                sparse matrix in CSR format when metric='precomputed'.
+                Ignored, present for API consistency with supervised learning.
+                Sample weights to use during clustering. If None, all samples are
+                treated equally.
+        Returns:
+                Fitted estimator.
+    fit_predict(X, y=None, sample_weight=None)
+        Fit the DBSCAN model and return cluster labels directly.
+        Parameters:
+                Training input samples of shape [n_samples, n_features].
+                Ignored, present for API consistency.
+                Sample weights to use during clustering.
+        Returns:
+                Cluster labels for each sample in X. Negative values (-1) indicate
+                noise points that are not assigned to any cluster.
+    _more_tags()
+        Return metadata tags about the estimator, including whether it handles
+        pairwise metrics when metric='precomputed'.
+Examples:
+    &gt;&gt;&gt; from sklearn.cluster import DBSCAN
+    &gt;&gt;&gt; from sklearn.datasets import make_blobs
+    &gt;&gt;&gt; X, _ = make_blobs(n_samples=300, centers=4, random_state=42)
+    &gt;&gt;&gt; clustering = DBSCAN(eps=0.5, min_samples=10).fit(X)
+    4
+    &gt;&gt;&gt; # Using precomputed distance matrix
+    &gt;&gt;&gt; from scipy.spatial.distance import cdist
+    &gt;&gt;&gt; dist_matrix = cdist(X, X, metric='euclidean')
+    &gt;&gt;&gt; clustering = DBSCAN(eps=0.5, min_samples=10, metric='precomputed').fit(dist_matrix)
+See Also:
+References:
+    [1] Ester, M., et al. "A Density-Based Algorithm for Discovering Clusters in Large Databases."
+        KDD 1996.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -6547,7 +7121,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>DepthwiseConv2D layer that applies a single filter per input channel.
+This layer implements depthwise convolution operations where each input channel
+is convolved independently with its own filter. The output has the same number
+of channels as the input multiplied by the depth_multiplier parameter.
+Attributes:
+        kernel (height, width).
+        dimensions. Default is (1, 1).
+        shape matches input shape except for batch and channel dimensions.
+        each input channel produces. Default is 1.
+        the channel dimension is first or last in the tensor.
+        and width dimensions. Default is (1, 1).
+Raises:
+Returns:
+        activation function. The output shape depends on input dimensions,
+        kernel size, strides, padding, and depth_multiplier.
+Examples:
+    &gt;&gt;&gt; layer = DepthwiseConv2D(kernel_size=3, strides=1, padding='same',
+    ...                         depth_multiplier=1)
+    &gt;&gt;&gt; outputs = layer(inputs)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -6878,7 +7470,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Embedding Layer for mapping discrete input indices to dense vector representations.
+This layer maps integer inputs (e.g., word indices) to dense vectors of fixed size.
+It is commonly used in natural language processing tasks where token indices are
+converted to embedding vectors that can be processed by subsequent layers.
+The layer creates an internal weight matrix of shape (input_dim, output_dim),
+where each row represents the embedding for a specific input index.
+Attributes:
+Args:
+        Represents the number of unique tokens or indices that can be embedded.
+        Each row in the embeddings matrix will have this many features.
+        Initializer for the weight matrix. Default is 'uniform'.
+        Regularizer to apply to the embedding weights.
+        Regularizer to apply to the output activations.
+        Constraint to apply to the embedding weights.
+        This is useful when working with variable-length sequences where padding
+        positions should be ignored during computation.
+        If provided, ensures all inputs have this exact sequence length.
+        If None, variable length sequences are supported.
+Returns:
+        (batch_size, output_dim) if input_length is not specified and inputs are 1D.
+        Each position in the output corresponds to an embedding vector for the
+        corresponding input index.
+Raises:
+Examples:
+    &gt;&gt;&gt; # Create an embedding layer with 1000 vocabulary and 64-dim embeddings
+    &gt;&gt;&gt; embedding = Embedding(input_dim=1000, output_dim=64)
+    &gt;&gt;&gt; 
+    &gt;&gt;&gt; # Use with a model for NLP tasks
+    &gt;&gt;&gt; model = tf.keras.Sequential([
+    ...     Embedding(input_dim=vocab_size, output_dim=embedding_dim),
+    ...     tf.keras.layers.GlobalAveragePooling1D(),
+    ...     tf.keras.layers.Dense(num_classes)
+    ... ])
+See Also:
+    - tf.keras.layers.Embedding for TensorFlow 2.x documentation
+    - tf.keras.preprocessing.sequence.pad_sequences for padding sequences</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8270,7 +8897,114 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Flask application factory class that provides a high-level interface for creating web applications.
+This class implements the Flask application pattern, providing routing, request/response handling, template rendering, static file serving, session management, and WSGI integration capabilities. It extends Werkzeug's BaseApplication with Flask-specific features including Jinja2 templating, blueprints support, error handling, and development server functionality.
+Attributes:
+Methods:
+        Initialize a Flask application with the given name and configuration options.
+        Args:
+        Raises:
+        Get the maximum age (in seconds) for send file headers based on configuration.
+        Args:
+        Returns:
+        Serve a static file from the configured static folder.
+        Args:
+        Returns:
+        Raises:
+        Open a resource from the application's root path.
+        Args:
+        Returns:
+        Raises:
+        Open a resource from the application's instance path.
+        Args:
+        Returns:
+    create_jinja_environment(self) -&gt; Environment
+        Create and configure the Jinja2 template environment for this application.
+        Returns:
+        Create a URL adapter for building URLs based on the current request or configuration.
+        Args:
+        Returns:
+        Raise a routing exception with debug-specific handling.
+        Args:
+        Raises:
+        Update template context with values from blueprint and application context processors.
+        Args:
+    make_shell_context(self) -&gt; dict[str, Any]
+        Create a shell context for the Flask CLI with app, g, and other context processors.
+        Returns:
+        Run the application's development server.
+        Args:
+        Raises:
+        Create a test client for testing the application without a server.
+        Args:
+        Returns:
+        Create a CLI runner for testing command-line interface commands.
+        Args:
+        Returns:
+        Handle an HTTP exception and optionally return a formatted response.
+        Args:
+        Returns:
+        Handle user exceptions, including Bad Request and HTTP exceptions.
+        Args:
+        Returns:
+        Raises:
+        Handle any exception during request processing.
+        Args:
+        Returns:
+        Log an exception that occurred during request processing.
+        Args:
+    dispatch_request(self) -&gt; ResponseReturnValue
+        Dispatch a request to the appropriate view function based on URL routing.
+        Returns:
+    full_dispatch_request(self) -&gt; Response
+        Execute the full request processing lifecycle including preprocessing, dispatching, and finalizing.
+        Returns:
+        Finalize a request by creating and processing the response.
+        Args:
+        Returns:
+    make_default_options_response(self) -&gt; Response
+        Create a default OPTIONS response for the current endpoint.
+        Returns:
+        Ensure a function is synchronous by converting async functions if necessary.
+        Args:
+        Returns:
+        Convert an async function to a synchronous one using asgiref.
+        Args:
+        Returns:
+        Raises:
+        Build a URL for the given endpoint with optional parameters.
+        Args:
+        Returns:
+        Raises:
+        Convert a view function return value into a Response object.
+        Args:
+        Returns:
+        Raises:
+    preprocess_request(self) -&gt; ResponseReturnValue | None
+        Execute before_request functions and return early if one returns a non-None value.
+        Returns:
+        Execute after_request functions and save the session before returning the response.
+        Args:
+        Returns:
+        Execute teardown functions registered for request context cleanup.
+        Args:
+        Execute teardown functions registered for app context cleanup.
+        Args:
+    app_context(self) -&gt; AppContext
+        Create an application context object for the current app.
+        Returns:
+        Create a request context object from the given WSGI environment.
+        Args:
+        Returns:
+        Create a test request context from an EnvironBuilder.
+        Args:
+        Returns:
+        The WSGI application callable that processes requests and returns responses.
+        Args:
+        Returns:
+        The main application entry point that delegates to wsgi_app.
+        Args:
+        Returns:</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -8804,7 +9538,83 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Transformer that applies a function to input data.
+This transformer applies an arbitrary callable function to the input data
+without requiring a fit step. It can also apply an inverse transformation
+using a separate inverse function, making it suitable for reversible
+transformations like standardization or encoding/decoding operations.
+Parameters
+----------
+    A callable that takes an array-like input and returns transformed data.
+    If None, the identity function is used (no transformation).
+    A callable that performs the inverse transformation on the output of
+    `func`. If None, no inverse transformation is available.
+    When True, inputs are validated according to scikit-learn standards.
+    Whether to accept sparse matrix inputs. If False, dense arrays are required.
+    Whether to verify that `func` and `inverse_func` are strict inverses of
+    each other when both are provided. Raises a warning if they are not.
+    How to determine output feature names:
+        - If callable, should accept two arguments (transformer and input
+          feature names) and return an array-like of output feature names.
+        - If "one-to-one", output feature names match input feature names.
+        - If None, no feature name handling is performed.
+    Keyword arguments to pass to `func` during transformation.
+    Keyword arguments to pass to `inverse_func` during inverse transformation.
+Attributes
+----------
+    The function used for transformation (same as `func`).
+    The function used for inverse transformation (same as `inverse_func`).
+    Whether validation is enabled (same as `validate`).
+    Whether sparse inputs are accepted (same as `accept_sparse`).
+    Whether inverse consistency checking is enabled (same as `check_inverse`).
+    The feature names output configuration (same as `feature_names_out`).
+Methods
+-------
+fit(X, y=None)
+    Stateless fit method. Returns self without modification since no learning
+    is required for this transformer.
+transform(X)
+    Apply the transformation function to input data X. Returns transformed
+    array-like or DataFrame depending on output configuration.
+inverse_transform(X)
+    Apply the inverse transformation function to input data X. Only works
+get_feature_names_out(input_features=None)
+    Get names of output features. Returns an array-like of feature names.
+set_output(transform=None)
+    Configure the output format for transform/inverse_transform methods.
+    Can be set to 'pandas', 'polars', or None (default numpy arrays).
+Returns
+-------
+    Returns self after fit (stateless transformer).
+Raises
+------
+ValueError
+    If `feature_names_out` is invalid (not callable, "one-to-one", or None).
+    If output column names don't match expected feature names when both are
+    provided and incompatible.
+UserWarning
+    When `check_inverse=True` and the functions are not strict inverses of
+    each other (only if inverse consistency check is enabled).
+See Also
+--------
+Examples
+--------
+&gt;&gt;&gt; from sklearn.compose import FunctionTransformer
+&gt;&gt;&gt; import numpy as np
+&gt;&gt;&gt; X = np.array([[1, 2], [3, 4]])
+&gt;&gt;&gt; ft.fit(X)
+FunctionTransformer()
+&gt;&gt;&gt; ft.transform(X)
+array([[ 1,  4],
+       [ 9, 16]])
+&gt;&gt;&gt; # With inverse transformation
+&gt;&gt;&gt; ft_inv = FunctionTransformer(
+... )
+&gt;&gt;&gt; ft_inv.fit(X)
+FunctionTransformer()
+&gt;&gt;&gt; ft_inv.inverse_transform(ft.transform(X))
+array([[1, 2],
+       [3, 4]])</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -9382,7 +10192,80 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Gaussian Mixture Model with different covariance types.
+This class implements a Gaussian Mixture Model using the Expectation-Maximization
+(EM) algorithm for parameter estimation. It supports multiple covariance matrix
+spherical (isotropic).
+The model can be initialized with pre-specified parameters or learned from data
+using k-means initialization. Supports warm-starting to continue training from
+previously fitted models.
+Parameters
+----------
+    Number of Gaussian components in the mixture. Must be at least 1.
+    Type of covariance matrix for each component. Options:
+    Convergence tolerance for the EM algorithm. Training stops when the
+    log-likelihood gain is less than this threshold.
+    Regularization added to the diagonal of the covariance matrices. Helps
+    prevent numerical issues with singular or near-singular matrices.
+    Maximum number of iterations for the EM algorithm.
+    Number of initializations with different random seeds. The best model
+    (highest log-likelihood) is returned.
+    Method for initializing component parameters:
+    Other options may be supported depending on parent class implementation.
+    Optional initial weights for each component. If None, weights are learned
+    Optional initial means for each component. If None, means are initialized
+    Optional initial precision matrices (inverse covariance). If None,
+    precisions are computed from covariances during initialization. Shape
+    depends on covariance_type.
+    Seed for random number generation. Use for reproducible results across
+    different runs.
+    Whether to use previously fitted parameters as starting point. If True,
+    training continues from existing state rather than re-initializing.
+    Verbosity level. 0 = no output, &gt;0 = progress messages every verbose_interval
+    iterations.
+    Interval for printing verbose output when verbose &gt; 0.
+Attributes
+----------
+    Weights of each component in the mixture. Sum to 1.
+    Mean vectors for each Gaussian component.
+    Covariance matrices for each component. Shape depends on covariance_type:
+    Cholesky decomposition of precision matrices for efficient computation.
+    Shape depends on covariance_type.
+    Full precision matrices (inverse covariances). Only computed when
+    covariance_type is 'full' or 'tied'. For 'diag' and 'spherical', this
+    attribute may not be available.
+    Number of components in the mixture (same as n_components).
+Methods
+-------
+    Fit the Gaussian Mixture Model to data X with optional class labels y.
+    Compute the log-likelihood of the data under the fitted model.
+    Predict the component label for each sample in X.
+    Compute the posterior probability of each sample belonging to each
+    component.
+    Compute the Bayesian Information Criterion (BIC) for model selection.
+    Higher BIC indicates better trade-off between fit and complexity.
+    Compute the Akaike Information Criterion (AIC) for model selection.
+    Lower AIC indicates better model according to this criterion.
+    Number of features in the input data X.
+    Number of output components (same as n_components).
+See Also
+--------
+Examples
+--------
+&gt;&gt;&gt; from sklearn.mixture import GaussianMixture
+&gt;&gt;&gt; X = np.random.randn(100, 2)
+&gt;&gt;&gt; gmm = GaussianMixture(n_components=2, random_state=0)
+&gt;&gt;&gt; gmm.fit(X)
+&gt;&gt;&gt; print(gmm.weights_)
+&gt;&gt;&gt; print(gmm.means_)
+&gt;&gt;&gt; print(gmm.predict_proba(X))
+Notes
+-----
+- The EM algorithm may converge to a local optimum. Use n_init &gt; 1 to run
+  multiple initializations and select the best solution.
+- For high-dimensional data, consider using 'diag' or 'spherical' covariance
+  types to reduce computational complexity.
+- The model assumes that data points are generated from a mixture of Gaussians</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -9538,7 +10421,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>GlobalAveragePooling1D Layer.
+This layer performs global average pooling over the last spatial dimension 
+of 1D inputs (sequences), reducing them to a single value per channel. 
+It is commonly used after 1D convolutions or RNN layers to produce fixed-size 
+representations from variable-length sequences.
+Attributes:
+        sequence data, default is True.
+Parameters:
+        For 1D inputs with shape (batch_size, steps, channels), this determines
+        the axis along which pooling occurs. Default is 'channels_last'.
+        GlobalPooling1D for initialization.
+Returns:
+        average-pooled values across the sequence dimension.
+Raises:
+Examples:
+    &gt;&gt;&gt; # Create a global average pooling layer for channels-last format
+    &gt;&gt;&gt; layer = GlobalAveragePooling1D()
+    &gt;&gt;&gt; 
+    &gt;&gt;&gt; # Apply to input tensor of shape (batch, steps, channels)
+Note:
+    - When mask is provided, the layer computes a weighted average where masked
+      positions contribute zero to both numerator and denominator.
+    - This layer is particularly useful for converting variable-length sequence
+      inputs into fixed-size feature vectors for classification tasks.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -9661,7 +10567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Computes global average pooling over the last two dimensions of the input tensor.
+This method performs global average pooling by computing the mean value across
+the spatial dimensions (height and width) of the input, preserving the batch
+and channel dimensions. The axis selection depends on the `data_format` attribute.
+Args:
+        `(batch, channels, height, width)` depending on `data_format`. This
+        represents the 2D input data (typically image features) to be pooled.
+Returns:
+        value computed across all spatial positions for each channel. The output
+        preserves the batch dimension and reduces height and width dimensions
+        to a single value per channel.
+Raises:
+Examples:
+    &gt;&gt;&gt; # Example with channels_last format (default)
+    &gt;&gt;&gt; layer = GlobalAveragePooling2D()
+    &gt;&gt;&gt; input_shape = (32, 32, 3)  # height, width, channels
+    &gt;&gt;&gt; # Example with channels_first format
+    &gt;&gt;&gt; layer = GlobalAveragePooling2D(data_format='channels_first')
+    &gt;&gt;&gt; input_shape = (3, 32, 32)  # channels, height, width
+Note: This method is part of the Keras Layer interface. The `call` method is
+automatically invoked when the layer is applied to input tensors in a model.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -9776,7 +10702,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Compute global average pooling over the last 4 dimensions of the input tensor.
+This layer performs global average pooling on 3D spatial data by computing the mean
+of each channel across all spatial dimensions (height, width, depth). The resulting
+tensor has shape (batch_size, num_channels) for 'channels_last' format or
+(batch_size, num_channels, 1, 1, 1) when keepdims is True.
+Args:
+        Determines which axes represent spatial dimensions.
+        Default is False, resulting in shape (batch_size, num_channels).
+Returns:
+        Shape depends on data_format and keepdims parameter settings.
+Raises:
+Examples:
+    &gt;&gt;&gt; layer = GlobalAveragePooling3D(data_format='channels_last', keepdims=False)
+    &gt;&gt;&gt; layer = GlobalAveragePooling3D(data_format='channels_first', keepdims=True)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -9911,7 +10850,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Perform global maximum pooling over a 1D input tensor.
+Global max pooling reduces all spatial dimensions of the input to a single value,
+keeping only the maximum value along those dimensions. This is commonly used in
+1D convolutional neural networks for feature extraction and dimensionality reduction.
+Args:
+        (batch_size, sequence_length) for 'channels_last' format or
+        (batch_size, channels, sequence_length) for other formats. The tensor must
+        be compatible with backend operations.
+Returns:
+        be reduced along spatial dimensions but maintained with size 1; otherwise,
+        spatial dimensions are fully collapsed. Shape is typically (batch_size, 1) or
+        (batch_size, channels, 1) depending on data format and keepdims setting.
+Raises:
+        unsupported operations.
+Examples:
+    &gt;&gt;&gt; # Global max pooling with channels_last format
+    &gt;&gt;&gt; layer = GlobalMaxPooling1D(data_format='channels_last', keepdims=True)
+    &gt;&gt;&gt; # Global max pooling with channels_first format
+    &gt;&gt;&gt; layer = GlobalMaxPooling1D(data_format='channels_first', keepdims=False)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -10034,7 +10991,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Perform global maximum pooling on input tensors.
+This layer computes the maximum value along specified spatial dimensions of the
+input tensor, effectively reducing the spatial size to a single value per channel.
+Args:
+            Expected shape depends on data_format setting:
+Returns:
+        be reduced along the spatial axes specified by data_format. If
+        keepdims=True, the output will have the same number of dimensions as
+        the input; otherwise, the pooled dimensions are squeezed out.
+Raises:
+Examples:
+    &gt;&gt;&gt; # For channels_last format (default in Keras)
+    &gt;&gt;&gt; layer = GlobalMaxPooling2D()
+    &gt;&gt;&gt; output = layer(inputs)  # Reduces height and width to 1
+    &gt;&gt;&gt; # For channels_first format
+    &gt;&gt;&gt; layer = GlobalMaxPooling2D(data_format='channels_first')
+    &gt;&gt;&gt; output = layer(inputs)  # Reduces height and width to 1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -10149,7 +11122,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Perform global max pooling on 3D input tensor.
+Applies a global maximum pooling operation to reduce the spatial dimensions of the
+input tensor, keeping only the maximum value across specified axes. The axis selection
+depends on the data format configuration.
+Args:
+        'channels_last' or (batch_size, height, width, channels) for 'channels_first'.
+Returns:
+    Tensor. The output tensor after applying global max pooling. Shape is reduced
+    to (batch_size, 1, 1) for 'channels_last' or (batch_size, 1, 1) for
+    'channels_first' when keepdims=True, otherwise shape depends on the pooling
+    operation configuration.
+Raises:
+Note:
+    - When keepdims=True (default), output maintains batch dimension only.
+    - Global max pooling computes the maximum value across all spatial dimensions.
+    - The axis selection adapts based on data_format to ensure consistent behavior.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -10249,7 +11237,43 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>GlobalPooling1D performs global pooling operations on 3D input tensors.
+This layer reduces the spatial dimensions (height and width) of the input tensor
+to a single value by performing either max or average pooling across all spatial
+positions. It is commonly used in CNN architectures to convert feature maps to
+Attributes:
+        Data format convention for channel ordering. Either 'channels_last' 
+        (default) or 'channels_first'. For 'channels_last', the shape is 
+        [batch, height, width, channels]. For 'channels_first', the shape is 
+        [batch, channels, height, width].
+        Whether to keep the spatial dimensions as size 1 after pooling. If True,
+        the output will have an additional dimension of size 1 for each reduced
+        spatial dimension.
+Methods:
+    compute_output_shape(input_shape) -&gt; TensorShape
+        Computes and returns the output tensor shape given the input shape.
+        Args:
+                (excluding batch dimension). Should be [height, width, channels]
+                'channels_first'.
+        Returns:
+        Raises:
+    call(inputs) -&gt; Tensor
+        Abstract method that raises NotImplementedError. Subclasses must implement
+        the actual pooling operation (e.g., GlobalMaxPooling1D, GlobalAveragePooling1D).
+        Args:
+                (channels_last) or [batch, channels, height, width] 
+                (channels_first).
+        Returns:
+    get_config() -&gt; dict
+        Returns a dictionary containing the configuration of this layer for 
+        serialization and model reconstruction.
+        Returns:
+                additional attributes from the parent Layer class.
+        Example:
+            &gt;&gt;&gt; config = layer.get_config()
+Example Usage:
+    &gt;&gt;&gt; from tensorflow.keras.layers import GlobalPooling1D
+    &gt;&gt;&gt; global_pool = GlobalPooling1D(keepdims=True)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -10351,7 +11375,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Abstract base class for global pooling operations on 4D tensors.
+This layer provides the infrastructure for global pooling (mean, max, etc.) across
+spatial dimensions of input tensors. The actual pooling operation must be implemented
+by subclassing this class and overriding the `call()` method.
+The class supports both 'channels_first' and 'channels_last' data formats and allows
+control over whether output dimensions should be kept as 1 or removed after pooling.
+Parameters
+----------
+    A string indicating the data format for convolution operations. Can be either
+    `'channels_first'` (batch, channels, height, width) or `'channels_last'`
+    (batch, height, width, channels). Default is None, which uses the default
+    If True, output dimensions are kept as 1 after pooling across spatial axes.
+    If False, these dimensions are removed from the output shape. This affects
+    how the output tensor shape is computed in `compute_output_shape()`.
+Returns
+-------
+None
+Raises
+------
+NotImplementedError
+    Raised when `call()` method is invoked before being overridden by a subclass.
+Examples
+--------
+&gt;&gt;&gt; # Example usage (must be subclassed for actual pooling)
+&gt;&gt;&gt; from tensorflow.keras.layers import GlobalPooling2D, AveragePooling2D
+&gt;&gt;&gt; 
+&gt;&gt;&gt; class MyGlobalPooling(GlobalPooling2D):
+&gt;&gt;&gt;     def call(self, inputs):
+&gt;&gt;&gt;         return K.mean(inputs, axis=(1, 2))  # Implement pooling logic
+&gt;&gt;&gt; 
+&gt;&gt;&gt; layer = MyGlobalPooling(data_format='channels_first', keepdims=True)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -10451,7 +11505,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>GlobalPooling3D is an abstract Keras layer for performing global pooling operations on 5D tensors (batch, channels, height, width, depth).
+This layer reduces all spatial dimensions to a single value through pooling operations while optionally preserving dimensionality with keepdims parameter. It serves as a base class that must be subclassed with a concrete implementation of the call() method.
+    Attributes:
+            Controls whether channel dimension comes first or last in tensor layout.
+            If True, output shape retains all original dimensions with pooled values.
+            If False, spatial dimensions are completely removed from output shape.
+    Methods:
+        compute_output_shape(input_shape) -&gt; TensorShape
+            Computes and returns the output tensor shape based on input shape and parameters.
+        call(inputs) -&gt; Tensor
+            Abstract method that must be implemented by subclasses to define pooling behavior.
+        get_config() -&gt; dict
+            Returns layer configuration dictionary for serialization purposes.
+    Raises:
+    Examples:
+        &gt;&gt;&gt; # Create a global pooling layer with channels_last format
+        &gt;&gt;&gt; pooling = GlobalPooling3D(data_format='channels_last', keepdims=False)
+        &gt;&gt;&gt; 
+        &gt;&gt;&gt; # Compute output shape for input of shape (batch, channels, height, width, depth)
+        &gt;&gt;&gt; input_shape = (32, 64, 128, 128, 64)  # batch=32, channels=64, etc.
+        &gt;&gt;&gt; output_shape = pooling.compute_output_shape(input_shape)
+        &gt;&gt;&gt; print(output_shape.as_list())  # [32, 64] when keepdims=False
+    Note:
+        This layer is designed for 3D volumetric data processing (e.g., medical imaging).
+        Subclasses must implement the call() method to define specific pooling operations
+        such as global average pooling or global max pooling.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -10775,7 +11854,62 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>shift_size: int = 1, window_type: str = 'rolling') -&gt; None:
+    """Initialize the GroupTimeSeriesSplit cross-validator.
+    Parameters:
+            number of groups. If float, should be between 0.0 and 1.0. 
+            If int, represents the absolute number of groups for the test set.
+            If None, n_splits must be specified. Cannot be used with expanding window.
+            train_size must be specified.
+            to prevent data leakage. Default is 0.
+            Controls how many groups are skipped between consecutive splits.
+            Default is 1.
+            size windows or 'expanding' where training set grows with each split.
+    Raises:
+            'rolling' or 'expanding', if train_size is specified with expanding window,
+            or if there is insufficient data for the specified number of splits.
+    Examples:
+        &gt;&gt;&gt; from sklearn.model_selection import GroupTimeSeriesSplit
+        &gt;&gt;&gt; # Create splitter with 5 folds, 0.2 test size, 1 group gap
+        &gt;&gt;&gt; gts = GroupTimeSeriesSplit(n_splits=5, test_size=0.2, gap_size=1)
+        &gt;&gt;&gt; # Split data with groups
+        &gt;&gt;&gt; for train_idx, test_idx in gts.split(X, y, groups):
+        ...     model.fit(X[train_idx], y[train_idx])
+        ...     score = model.score(X[test_idx], y[test_idx])
+        &gt;&gt;&gt; # Create splitter with fixed training size
+        &gt;&gt;&gt; gts2 = GroupTimeSeriesSplit(train_size=100, test_size=50)
+    """
+          groups: array_like | None = None) -&gt; Generator[tuple[array_like, array_like], None, None]:
+    """Generate train/test splits for grouped time series data.
+    Yields:
+            samples for each split. Both indices are arrays of group indices.
+    Parameters:
+            (n_samples, n_outputs). Default is None.
+            integers starting from 0. Each group represents a temporal block 
+            that should be kept together in either training or test sets.
+    Raises:
+            or if there is insufficient data to generate the required number of splits.
+    Examples:
+        &gt;&gt;&gt; from sklearn.model_selection import GroupTimeSeriesSplit
+        &gt;&gt;&gt; gts = GroupTimeSeriesSplit(n_splits=5, test_size=0.2)
+        &gt;&gt;&gt; for train_idx, test_idx in gts.split(X, y, groups):
+    Note:
+        The groups parameter is required and must contain consecutive integers 
+        representing temporal blocks. Samples within the same group are treated 
+        as temporally related and will not be split between train and test sets.
+    """
+"""Return the number of splits generated by this cross-validator.
+    Parameters:
+            consistency with scikit-learn convention.
+            consistency with scikit-learn convention.
+            consistency with scikit-learn convention.
+    Returns:
+    Examples:
+        &gt;&gt;&gt; from sklearn.model_selection import GroupTimeSeriesSplit
+        &gt;&gt;&gt; gts = GroupTimeSeriesSplit(n_splits=5)
+        &gt;&gt;&gt; print(gts.get_n_splits())
+        5
+    """</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -11000,7 +12134,85 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>K-means clustering algorithm implementation.
+This class implements the K-means clustering algorithm for partitioning
+data into k clusters based on feature similarity. It inherits from base model,
+cluster, and iterative model classes to provide a consistent API.
+Attributes:
+Methods:
+Examples:
+    &gt;&gt;&gt; from sklearn.cluster import Kmeans
+    &gt;&gt;&gt; # Initialize with 3 clusters
+    &gt;&gt;&gt; kmeans = Kmeans(k=3, max_iter=10)
+    &gt;&gt;&gt; # Fit on training data
+    &gt;&gt;&gt; kmeans.fit(X_train)
+    &gt;&gt;&gt; # Predict cluster assignments for new data
+    &gt;&gt;&gt; predictions = kmeans.predict(X_test)
+"""
+int, max_iter: int = 10, convergence_tolerance: float = 1e-05, random_seed: int | None = None, print_progress: bool = False) -&gt; None:
+    """Initialize K-means clustering model.
+    Args:
+            Algorithm stops when centroids change less than this value. Default is 1e-05.
+            If None, uses system random state. Default is None.
+            Default is False.
+    Attributes:
+    Returns:
+    Raises:
+    Example:
+        &gt;&gt;&gt; from sklearn.cluster import Kmeans
+        &gt;&gt;&gt; model = Kmeans(k=5, max_iter=20, random_seed=42)
+        &gt;&gt;&gt; model.fit(X_train)
+    """
+    _BaseModel.__init__(self)
+    _Cluster.__init__(self)
+    _IterativeModel.__init__(self)
+np.ndarray, init_params: bool = True) -&gt; 'Kmeans':
+    """Fit the K-means clustering model to training data.
+    Args:
+            Each row represents a sample with features.
+            data samples. If False, uses existing centroids. Default is True.
+    Returns:
+    Attributes Set:
+    Raises:
+    Example:
+        &gt;&gt;&gt; model = Kmeans(k=3)
+        &gt;&gt;&gt; model.fit(X_train)
+        &gt;&gt;&gt; print(model.iterations_)
+        5
+    """
+    n_samples = X.shape[0]
+        rgen = np.random.RandomState(self.random_seed)
+        idx = rgen.choice(n_samples, self.k, replace=False)
+        new_centroids = np.array([np.mean(X[self.clusters_[k]], axis=0) for k in sorted(self.clusters_.keys())])
+            break
+        else:
+np.ndarray, centroids: np.ndarray):
+    """Generator yielding cluster index for each sample based on nearest centroid.
+    Args:
+    Yields:
+    Notes:
+        Uses Euclidean distance to determine cluster assignment.
+        Samples are assigned to the nearest centroid.
+    Example:
+        &gt;&gt;&gt; model = Kmeans(k=3)
+        &gt;&gt;&gt; model.fit(X_train)
+        &gt;&gt;&gt; for idx in model._get_cluster_idx(X=X_test, centroids=model.centroids_):
+        ...     print(idx)
+    """
+        dist = np.sqrt(np.sum(np.square(sample - self.centroids_), axis=1))
+        yield np.argmin(dist)
+np.ndarray) -&gt; np.ndarray:
+    """Predict cluster labels for new data samples.
+    Args:
+            Each row represents a sample to be clustered.
+    Returns:
+            Each value is an integer from 0 to k-1 representing the cluster assignment.
+    Raises:
+    Example:
+        &gt;&gt;&gt; model = Kmeans(k=3)
+        &gt;&gt;&gt; model.fit(X_train)
+        &gt;&gt;&gt; predictions = model.predict(X_test)
+        [0 2 1 0 2]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -11366,7 +12578,97 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Convert label data to binary format for machine learning tasks.
+This transformer converts target labels into binary representation (0/1)
+based on specified positive and negative thresholds. It supports both
+sparse and dense matrix outputs, and can handle multi-label classification
+scenarios.
+Parameters
+----------
+    The value representing the negative class in the input data.
+    Must be strictly less than pos_label. Default is 0.
+    The value representing the positive class in the input data.
+    Must be greater than neg_label. Default is 1.
+    Whether to return sparse matrix output. Only supported with
+    non-zero pos_label and zero neg_label.
+Attributes
+----------
+    Stored negative label value from fit().
+    Stored positive label value from fit().
+    Whether sparse output is enabled, stored after fit().
+    Unique labels found in the input data during fit().
+Methods
+-------
+    Fit the LabelBinarizer to target data. Validates input parameters
+    and determines the appropriate binarization strategy based on
+    the target type.
+    Parameters
+    ----------
+        Target values for fitting. Can be integer labels or boolean values.
+    Returns
+    -------
+        Fitted estimator instance.
+    Raises
+    ------
+    ValueError
+        If neg_label &gt;= pos_label, if multioutput target is detected,
+        or if input contains zero samples.
+    Fit the LabelBinarizer to target data and transform it in one step.
+    Parameters
+    ----------
+        Target values for fitting and transformation.
+    Returns
+    -------
+        Binary representation of the input labels.
+    Transform target data using the fitted binarizer configuration.
+    Parameters
+    ----------
+        Target values to transform. Must be compatible with the
+        fitted estimator's configuration.
+    Returns
+    -------
+        Binary representation of the input labels.
+    Raises
+    ------
+    ValueError
+        If the transformer was not fitted with multilabel input when
+        transforming multilabel data.
+    Convert binary representation back to original label format.
+    Parameters
+    ----------
+        Binary values to convert back to original labels.
+        Threshold for converting binary values back to original labels.
+        If None, uses the average of pos_label and neg_label.
+    Returns
+    -------
+        Original label representation from binary data. The output format
+        matches the input type used during fit() (sparse or dense).
+    Raises
+    ------
+    ValueError
+        If the transformer was not fitted before calling inverse_transform.
+Examples
+--------
+&gt;&gt;&gt; from sklearn.preprocessing import LabelBinarizer
+&gt;&gt;&gt; lb = LabelBinarizer(pos_label=1, neg_label=0)
+&gt;&gt;&gt; y = [0, 1, 2, 3]
+&gt;&gt;&gt; Y = lb.fit_transform(y)
+&gt;&gt;&gt; print(Y)
+[[1 0 0 0]
+ [0 1 0 0]
+ [0 0 1 0]
+ [0 0 0 1]]
+&gt;&gt;&gt; y_inv = lb.inverse_transform(Y)
+&gt;&gt;&gt; print(y_inv)
+[0 1 2 3]
+&gt;&gt;&gt; # Using sparse output
+&gt;&gt;&gt; lb_sparse = LabelBinarizer(pos_label=1, neg_label=0, sparse_output=True)
+&gt;&gt;&gt; Y_sparse = lb_sparse.fit_transform(y)
+&gt;&gt;&gt; from scipy import sparse
+&gt;&gt;&gt; print(sparse.issparse(Y_sparse))
+True
+See Also
+--------</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -11594,7 +12896,55 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Fit the LabelEncoder to learn classes from target values.
+        Learn the unique classes present in the input data and store them
+        Args:
+                to be encoded. Will be converted to a 1D column if necessary.
+        Returns:
+        Attributes:
+        """
+        """Fit the encoder and transform the labels in one step.
+        Fit the LabelEncoder to learn classes from target values, then
+        immediately transform the input using the learned encoding. This is
+        equivalent to calling fit() followed by transform().
+        Args:
+                to be encoded and transformed. Will be converted to a 1D
+                column if necessary.
+        Returns:
+                to its corresponding index in the learned classes_.
+        Note:
+            The returned values are indices into self.classes_, not the
+            original labels. Use inverse_transform() to recover original
+            categorical values.
+        """
+        """Transform labels to encoded integer indices.
+        Encode input labels using the classes learned during fit(). Each
+        unique label is mapped to a consistent integer index.
+        Args:
+                present in self.classes_ when transform() is called on an
+                already fitted encoder. Will be converted to a 1D column
+        Returns:
+                label. If input contains no samples, returns empty array.
+        Raises:
+                fit_transform() before calling transform().
+        Note:
+            This method requires the encoder to be fitted first. Empty
+            input arrays are handled gracefully by returning an empty array.
+        """
+        """Transform encoded integer indices back to original labels.
+        Convert encoded integer values back to their original categorical
+        label representations using the learned classes mapping.
+        Args:
+                converted to a 1D column if necessary. Values must be valid
+                indices into self.classes_.
+        Returns:
+                corresponding to the input encoded indices.
+        Raises:
+                indices into self.classes_ (i.e., previously unseen labels).
+        Note:
+            Only works on an already fitted encoder. Empty input arrays
+            are handled gracefully by returning an empty array.
+        """</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -11905,7 +13255,171 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>str = 'direct', eta: float = 0.01, epochs: int = 50, minibatches: Optional[int] = None, random_seed: Optional[int] = None, print_progress: bool = False) -&gt; None:
+    """Initialize the LinearRegression model with specified parameters.
+    Parameters
+    ----------
+        The fitting algorithm to use. Valid options are 'sgd', 'direct', 
+        'svd', or 'qr'. The 'direct' method uses the normal equation for
+        closed-form solution, while 'sgd' uses stochastic gradient descent.
+        Learning rate for SGD optimization. Controls step size during
+        parameter updates. Higher values may converge faster but risk
+        overshooting the minimum.
+        Number of training epochs for SGD method. Each epoch processes
+        all samples (or minibatches) once through the dataset.
+        Minibatch size for SGD optimization. When specified, data is
+        split into chunks of this size for each iteration. Must be None
+        when using methods other than 'sgd'. Set to number of samples
+        Random seed for reproducibility in SGD initialization and shuffling.
+        If None, uses system randomness which may lead to non-reproducible
+        results across different runs.
+        Whether to print training progress during SGD. When True, displays
+        epoch number and cost after each iteration. Can also be an integer
+        to print at specific iterations.
+    Attributes
+    ----------
+        Final learning rate used (may differ from initial if modified).
+        Number of epochs actually used for training.
+        Minibatch size actually used for training.
+        Random seed that was used for reproducibility.
+        Whether progress printing is enabled.
+        The fitting method that was actually used.
+        Training costs recorded during SGD optimization. Empty for other
+        methods or when init_params=False.
+    Raises
+    ------
+    ValueError
+        If minibatches is not None when method is not 'sgd'.
+        If method is not one of the supported algorithms ('sgd', 'direct',
+        'svd', 'qr').
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.linear_model import LinearRegression
+    &gt;&gt;&gt; model = LinearRegression(method='direct')  # Use normal equation
+    &gt;&gt;&gt; model = LinearRegression(method='sgd', eta=0.1, epochs=100)  # SGD
+    """
+    _BaseModel.__init__(self)
+    _IterativeModel.__init__(self)
+    _Regressor.__init__(self)
+        raise ValueError('Minibatches should be set to `None` if `method` != `sgd`. Got method=`%s`.' % method)
+    supported_methods = ('sgd', 'direct', 'svd', 'qr')
+        raise ValueError('`method` must be in %s. Got %s.' % (supported_methods, method))
+"""Fit the model using training data with specified algorithm.
+    This private method handles the actual fitting process for all supported
+    algorithms. It initializes parameters if requested and applies the selected
+    fitting method (normal equation, SGD, QR decomposition, or SVD).
+    Parameters
+    ----------
+        Training samples where each row is a sample and each column is a feature.
+        Target values for regression task. Can be 1D for single output or
+        2D for multi-output regression.
+        Whether to initialize model parameters before fitting. If False, uses
+        existing parameters which must have been set manually.
+    Attributes
+    ----------
+        Fitted bias term (intercept) for the regression model.
+        Fitted weights for each feature in the model.
+        Training costs recorded during optimization. Contains one value per
+        epoch when using SGD method. Empty list for other methods.
+        Start time of training (only set for SGD method).
+    Returns
+    -------
+        Fitted estimator instance for method chaining.
+    Notes
+    -----
+      This is computationally expensive O(n^3) but provides exact solution.
+    - The 'sgd' method iteratively updates weights using gradient descent.
+      Cost values are recorded after each epoch for monitoring convergence.
+    - The 'qr' and 'svd' methods provide numerically stable alternatives
+      that work well when X^T X is ill-conditioned.
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.linear_model import LinearRegression
+    &gt;&gt;&gt; model = LinearRegression(method='direct')
+    &gt;&gt;&gt; model.fit(X_train, y_train)  # Uses normal equation
+    &gt;&gt;&gt; model_sgd = LinearRegression(method='sgd', epochs=100)
+    &gt;&gt;&gt; model_sgd.fit(X_train, y_train)  # Uses SGD with cost tracking
+    """
+    elif self.method == 'sgd':
+        rgen = np.random.RandomState(self.random_seed)
+                y_val = self._net_input(X[idx])
+                errors = y[idx] - y_val
+            cost = self._sum_squared_error_cost(y, self._net_input(X))
+    elif self.method == 'qr':
+        Xb = np.hstack((np.ones((X.shape[0], 1)), X))
+        Q, R = np.linalg.qr(Xb)
+        beta = np.dot(np.linalg.inv(R), np.dot(Q.T, y))
+    elif self.method == 'svd':
+        Xb = np.hstack((np.ones((X.shape[0], 1)), X))
+        beta = np.dot(np.linalg.pinv(Xb), y)
+"""Compute regression coefficients using the normal equation.
+    This method implements the closed-form solution for linear regression:
+    w = (X^T X)^-1 X^T y
+    Parameters
+    ----------
+        Training samples without bias term included.
+        Target values for regression task.
+    Returns
+    -------
+        Computed bias term (intercept).
+        Computed weight coefficients for each feature.
+    Notes
+    -----
+    This method is used when `method='direct'`. It adds a column of ones
+    to X to handle the bias term, solves the normal equation, and returns
+    both bias and weights separately. May raise LinAlgError if X^T X is
+    singular or nearly singular (ill-conditioned).
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.linear_model import LinearRegression
+    &gt;&gt;&gt; model = LinearRegression(method='direct')
+    &gt;&gt;&gt; b, w = model._normal_equation(X_train, y_train)
+    """
+    Xb = np.hstack((np.ones((X.shape[0], 1)), X))
+    w = np.zeros(X.shape[1])
+    z = np.linalg.inv(np.dot(Xb.T, Xb))
+    params = np.dot(z, np.dot(Xb.T, y))
+"""Compute predictions for given samples using fitted model.
+    This method computes the linear prediction z = X @ w + b for input samples.
+    The output is flattened to maintain consistency with scikit-learn interface.
+    Parameters
+    ----------
+        Samples for which to compute predictions.
+    Returns
+    -------
+        Predicted values for each sample in the input array.
+    Notes
+    -----
+    This method is used internally by `_predict` and during SGD optimization
+    to compute prediction errors. The weights must be fitted before calling
+    this method.
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.linear_model import LinearRegression
+    &gt;&gt;&gt; model = LinearRegression()
+    &gt;&gt;&gt; model.fit(X_train, y_train)
+    &gt;&gt;&gt; predictions = model._net_input(X_test)
+    """
+"""Make predictions for new samples using the fitted model.
+    This method delegates to `_net_input` to compute predictions for input
+    samples. It assumes the model has been fitted previously.
+    Parameters
+    ----------
+        Samples for which to compute predictions.
+    Returns
+    -------
+        Predicted values for each sample in the input array.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted yet (check `_is_fitted` attribute).
+    Examples
+    --------
+    &gt;&gt;&gt; from sklearn.linear_model import LinearRegression
+    &gt;&gt;&gt; model = LinearRegression(method='direct')
+    &gt;&gt;&gt; model.fit(X_train, y_train)
+    &gt;&gt;&gt; predictions = model.predict(X_test)
+    """</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -12190,7 +13704,78 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Logistic Regression model using gradient descent with L2 regularization.
+This class implements binary logistic regression with support for mini-batch
+stochastic gradient descent, L2 regularization, and configurable training
+parameters. The model learns to classify samples into two classes (0 or 1)
+using the sigmoid activation function on a linear combination of features.
+Attributes:
+Methods:
+Example:
+    &gt;&gt;&gt; model = LogisticRegression(eta=0.01, epochs=100, l2_lambda=0.01)
+    &gt;&gt;&gt; model.fit(X_train, y_train)
+    &gt;&gt;&gt; predictions = model.predict(X_test)
+    &gt;&gt;&gt; probabilities = model.predict_proba(X_test)
+"""
+float = 0.01, epochs: int = 50, l2_lambda: float = 0.0, minibatches: int = 1, random_seed: int | None = None, print_progress: bool = False):
+    """Initialize the LogisticRegression model with specified hyperparameters.
+    Args:
+            Default is 0.0.
+    Attributes:
+    Returns:
+    Raises:
+    """
+np.ndarray) -&gt; np.ndarray:
+    """Compute forward pass through the network with sigmoid activation.
+    Args:
+    Returns:
+            Shape is (n_samples,) for binary classification.
+    """
+np.ndarray, y_true: np.ndarray, y_probas: np.ndarray) -&gt; tuple[np.ndarray, np.ndarray]:
+    """Compute gradients of loss with respect to weights and bias.
+    Args:
+    Returns:
+            where grad_loss_wrt_w is weight gradient and grad_loss_wrt_b is bias gradient.
+    Raises:
+    """
+np.ndarray, y: np.ndarray, init_params: bool = True) -&gt; 'LogisticRegression':
+    """Train the model using mini-batch stochastic gradient descent.
+    Args:
+    Returns:
+    Raises:
+    Notes:
+        - Training cost is tracked in self.cost_ list.
+        - Progress can be printed during training if print_progress is set.
+        - L2 regularization is applied to weights during each update step.
+    """
+np.ndarray) -&gt; np.ndarray:
+    """Predict class labels (0 or 1) for input samples.
+    Args:
+    Returns:
+    Raises:
+    """
+np.ndarray) -&gt; np.ndarray:
+    """Compute linear combination of features and weights without activation.
+    Args:
+    Returns:
+    """
+np.ndarray) -&gt; np.ndarray:
+    """Return probability estimates for each class.
+    Args:
+    Returns:
+            Values are in range [0, 1]. Higher values indicate higher probability of class 1.
+    Raises:
+    """
+np.ndarray, y_val: np.ndarray) -&gt; float:
+    """Compute binary cross-entropy loss with optional L2 regularization.
+    Args:
+    Returns:
+    Notes:
+    """
+np.ndarray) -&gt; np.ndarray:
+    """Apply sigmoid activation function to input values.
+    Args:
+    Returns:</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -12378,7 +13963,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Base class for defining loss functions in Keras.
+This abstract class provides the interface for loss computation in Keras models.
+Subclasses must implement the `call()` method to define specific loss behavior.
+The class handles tensor conversion, masking, sample weighting, and reduction of
+loss values automatically through the `__call__` method.
+Attributes:
+        ('sum_over_batch_size' by default)
+Methods:
+Parameters:
+        Options include 'sum_over_batch_size' (default), 'mean', 'sum', etc.
+        float type (typically 'float32').
+Returns:
+        value is computed by calling `self.call()`, applying sample weights if
+        provided, and reducing according to the reduction strategy.
+        computation.
+Raises:
+        by a subclass.
+Examples:
+    &gt;&gt;&gt; from keras import losses
+    &gt;&gt;&gt; # Create a mean squared error loss
+    &gt;&gt;&gt; mse_loss = losses.MeanSquaredError()
+    &gt;&gt;&gt; # Compute loss with predictions and targets
+    &gt;&gt;&gt; loss_value = mse_loss(y_true, y_pred)
+    &gt;&gt;&gt; # Loss can be used in model compilation
+    &gt;&gt;&gt; model.compile(optimizer='adam', loss=mse_loss)
+See Also:</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -12548,7 +14158,18 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D Max Pooling Layer.
+This layer applies a max pooling operation over input data in the temporal dimension,
+reducing the spatial dimensions while preserving feature information. It is commonly
+used in convolutional neural networks for downsampling and reducing computational load.
+Args:
+        For 1D inputs, typically an integer (e.g., 2) representing the max pooling window size.
+        Default is 2.
+        If None, defaults to pool_size. Default is None.
+        or 'same' (pad to maintain spatial dimensions). Default is 'valid'.
+        the data format of the input tensors. Default is 'channels_last'.
+Returns:
+Raises:</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -12800,7 +14421,39 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Apply max pooling over a tensor of shape (batch_size, height, width, channels).
+This layer performs max pooling, which is commonly used to reduce the spatial
+dimensions of feature maps while preserving the most important features. It is
+typically used in convolutional neural networks for downsampling.
+Parameters
+----------
+    Factor by which to downscale the input dimensions. If an integer, it will
+    apply the same factor to both height and width. Default is (2, 2).
+    Strides for pooling. If None, defaults to pool_size. Can be a single integer
+    or a tuple of two integers.
+    Padding algorithm to use before pooling. Options are 'valid' (no padding)
+    or 'same' (padded to maintain input dimension).
+    'channels_last' (batch, height, width, channels). Default is None which
+    inherits from the backend.
+    Additional keyword arguments passed to the parent class initialization.
+Returns
+-------
+None
+    This method initializes the layer instance and returns None.
+Raises
+------
+ValueError
+    If pool_size, strides, padding, or data_format contains invalid values.
+Examples
+--------
+&gt;&gt;&gt; from tensorflow.keras.layers import MaxPooling2D
+&gt;&gt;&gt; # Create a max pooling layer with default settings
+&gt;&gt;&gt; layer = MaxPooling2D()
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Create with custom pool size and padding
+&gt;&gt;&gt; layer = MaxPooling2D(pool_size=(3, 3), padding='same')
+See Also
+--------</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -12936,7 +14589,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Applies a 3D max pooling operation over an input volume.
+This layer computes the maximum value over specified regions in 3D spatial
+dimensions (height, width, depth) of the input tensor. It is commonly used
+in 3D convolutional neural networks for feature extraction and dimensionality
+reduction.
+Args:
+        each pooling dimension. If None, uses pool_size as strides. Default is
+        None.
+        dimensions). Default is 'valid'.
+        determines the order of the dimensions in the input tensors. Default is
+        None (inferred from backend configuration).
+        Pooling3D initialization.
+Returns:
+    None
+Raises:</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13363,7 +15030,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Base class for all Keras metrics.
+This class provides common functionality for tracking metrics during model
+training and evaluation. All metric implementations should inherit from this
+The base class supports both stateful operations (standard variable-based)
+and stateless operations (for use in custom training loops or when variables
+need to be passed explicitly).
+Attributes:
+Methods:
+        input arguments. Must be implemented by subclasses.
+        by subclasses.
+    add_variable(shape, initializer, dtype=None, aggregation='sum', name=None):
+        Adds a new variable to track within this metric.
+Examples:
+    &gt;&gt;&gt; from keras import metrics
+    &gt;&gt;&gt; accuracy = metrics.MeanMetric(name='accuracy')
+    &gt;&gt;&gt; # Subclass would implement update_state and result methods</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -13793,7 +15475,65 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Converts a multi-label dataset into a binary indicator matrix.
+This transformer converts each sample's labels into a binary vector where each
+element corresponds to whether that label is present (1) or absent (0). The
+classes can be either provided explicitly or learned from the training data.
+Parameters
+----------
+    A list/set of classes to use for binarization. If None, classes are
+    automatically determined from the input labels and sorted alphabetically/numerically.
+    Whether to return a sparse matrix (scipy.sparse.csr_matrix) instead of
+    a dense numpy array. Useful for large datasets with many features.
+Attributes
+----------
+    The classes found in the training data or provided via `classes`.
+    Mapping from class values to their corresponding column indices.
+    Whether sparse output is enabled (same as `sparse_output` parameter).
+Methods
+-------
+fit(y)
+    Fit the MultiLabelBinarizer to multi-label data. Learns classes if not
+    provided, and builds internal mappings for transformation.
+fit_transform(y)
+    Convenience method that fits the transformer and transforms the input in one step.
+transform(y)
+    Transform new multi-label data using the fitted class mappings. Returns
+    either a sparse matrix or dense array based on `sparse_output`.
+inverse_transform(yt)
+    Convert a binary indicator matrix back to multi-label format. Each row
+    of the input matrix corresponds to one sample, with 1s indicating present labels.
+Notes
+-----
+- Unknown classes in transform() are ignored with a warning.
+- inverse_transform() requires the input matrix to have exactly len(classes_) columns.
+- Only 0 and 1 values are valid in the indicator matrix for inverse_transform().
+- The transformer supports both dense arrays and sparse matrices (CSR format).
+Examples
+--------
+&gt;&gt;&gt; from sklearn.preprocessing import MultiLabelBinarizer
+&gt;&gt;&gt; mlb = MultiLabelBinarizer()
+&gt;&gt;&gt; y = [['cat', 'dog'], ['dog'], ['cat', 'fish']]
+&gt;&gt;&gt; Y = mlb.fit_transform(y)
+&gt;&gt;&gt; print(Y)
+[[1 1 0]
+ [0 1 0]
+ [1 0 1]]
+&gt;&gt;&gt; print(mlb.classes_)
+['cat' 'dog' 'fish']
+&gt;&gt;&gt; # Using explicit classes and sparse output
+&gt;&gt;&gt; mlb_sparse = MultiLabelBinarizer(classes=['a', 'b', 'c'], sparse_output=True)
+&gt;&gt;&gt; Y_sparse = mlb_sparse.fit_transform([['a', 'b'], ['b', 'c'], ['a', 'c']])
+&gt;&gt;&gt; print(Y_sparse.toarray())
+[[1 1 0]
+ [0 1 1]
+ [1 0 1]]
+&gt;&gt;&gt; # Converting back to original format
+&gt;&gt;&gt; labels = mlb.inverse_transform(Y)
+&gt;&gt;&gt; print(labels)
+[['cat', 'dog'], ['dog'], ['cat', 'fish']]
+See Also
+--------</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -14955,7 +16695,55 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>OneHotEncoder encodes categorical features using one-hot encoding scheme.
+This encoder transforms categorical features into a binary representation where each category
+becomes a separate column. It supports handling of infrequent categories, dropping encoded
+columns to reduce dimensionality, and various strategies for handling unknown categories.
+Parameters
+----------
+    Categories (unique values) per feature:
+    The categories used to encode new data must match exactly the categories provided here.
+    Whether and how to drop encoded columns:
+    Whether to return a sparse matrix as output. If False, returns dense numpy array.
+    Desired output data type for the encoded features.
+    How to handle categories seen during transform that weren't in training data:
+    Minimum frequency threshold for categories to be considered frequent. Categories below
+    this threshold are grouped into an 'infrequent' category when infrequent handling is enabled.
+    Maximum number of categories per feature. If set, only the most frequent categories up to
+    this limit are kept, with less frequent ones grouped as infrequent.
+    Function or string used to combine feature name and category names when generating
+    feature names for output columns:
+Attributes
+----------
+    The categories seen during fit for each feature.
+    Indices of categories to drop after fitting.
+    The data type used for the encoded output.
+    Number of features passed to `fit`.
+    Number of features in the transformed output.
+See Also
+--------
+Examples
+--------
+&gt;&gt;&gt; from sklearn.preprocessing import OneHotEncoder
+&gt;&gt;&gt; import numpy as np
+&gt;&gt;&gt; X = [['Male', 1], ['Female', 3], ['Female', 2]]
+&gt;&gt;&gt; enc = OneHotEncoder(sparse_output=False)
+&gt;&gt;&gt; enc.fit(X)
+OneHotEncoder(...)
+&gt;&gt;&gt; enc.transform(X)
+array([[1., 0., 1., 0.],
+       [0., 1., 0., 1.],
+       [0., 1., 0., 0.]])
+Notes
+-----
+- The `categories` parameter can be set to 'auto' for automatic category detection, or
+  explicitly provided as a list of lists.
+- When `drop='if_binary'`, the second category is dropped if there are exactly two categories.
+- Infrequent category handling requires setting `min_frequency` and enables grouping rare
+  categories into a single 'infrequent' group.
+- For sparse output, ensure the data type is compatible with sparse matrix operations.
+References
+----------</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -15459,7 +17247,68 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>OPTICS clustering algorithm implementation.
+The OPTICS (Ordering Points To Identify the Clustering Structure) algorithm
+can discover clusters of arbitrary shape in datasets with varying densities.
+It is a generalization of DBSCAN that can handle clusters of different sizes
+and densities without requiring a single epsilon parameter.
+Parameters
+----------
+    The minimum number of samples in a neighborhood for a point to be
+    considered a core point. Must be at least 2.
+    Maximum epsilon value for the reachability plot. Used when eps is None.
+    The metric to use when calculating distance between instances in a feature
+    array. Can be 'precomputed' for precomputed distance matrices. Valid options
+    include 'euclidean', 'manhattan', 'minkowski', etc., or any callable with
+    signature ``metric(x, y)``.
+    Power parameter for the Minkowski metric. For p=2, this is equivalent to
+    Euclidean distance. For p=1, Manhattan distance. Must be at least 1.
+    Additional keyword arguments to pass to the metric function.
+    The clustering method to use on the reachability graph:
+    Epsilon parameter for DBSCAN clustering. If None, uses max_eps. Only used
+    when cluster_method='dbscan'. Must be less than or equal to max_eps.
+    aggressively clusters are merged in the reachability graph.
+    Whether to apply predecessor correction in the Xi clustering method.
+    The minimum number of points in a cluster. If None, no minimum is enforced.
+    Must be at least 2 if specified as integer.
+    Algorithm used to compute the condensed distance matrix:
+    Leaf size for ball tree and kd tree algorithms. Larger values may result
+    in slower computation but fewer memory accesses.
+    Path to the OS file where data/pickle should be stored for memory caching.
+    Use 'None' to avoid using memory cache.
+    The number of jobs to run in parallel. Only used when algorithm is not
+    'brute'. Use -1 to use all processors.
+Attributes
+----------
+    Cluster labels for each sample. Samples with label -1 are considered noise.
+    The ordering of points in the reachability plot.
+    Core distances for each point in the dataset.
+    Reachability distances for each point in the dataset.
+    Predecessor information for each point in the reachability graph.
+    Cluster hierarchy when cluster_method='xi'. Contains information about
+    nested clusters found by the algorithm.
+See Also
+--------
+Notes
+-----
+The OPTICS algorithm is a generalization of DBSCAN that does not require a
+single epsilon parameter and can discover clusters of arbitrary shape in
+datasets with varying densities. It produces a reachability plot that shows
+the order in which points are visited during the clustering process.
+When cluster_method='dbscan', the algorithm requires an eps parameter to
+define the neighborhood radius for core point identification. When
+cluster_method='xi', the algorithm can automatically determine appropriate
+epsilon values and find clusters of varying densities.
+Examples
+--------
+&gt;&gt;&gt; from sklearn.cluster import OPTICS
+&gt;&gt;&gt; from sklearn.datasets import make_blobs
+&gt;&gt;&gt; X, _ = make_blobs(n_samples=500, centers=4, random_state=42)
+&gt;&gt;&gt; clustering = OPTICS(min_cluster_size=10).fit(X)
+&gt;&gt;&gt; print(clustering.labels_)
+References
+----------
+    SIGMOD 1999.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -16116,7 +17965,94 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Encode categorical features into ordinal values for machine learning models.
+This encoder transforms categorical features into numeric ordinal representations,
+handling missing values and unknown categories according to specified configuration.
+Parameters
+----------
+    How the categories should be determined. If 'auto', uses all unique values
+    in each feature. Can also be a list of lists where each inner list contains
+    the categories for that feature.
+    The data type to use for encoded values. For missing value encoding with
+    np.nan, this must be a float dtype.
+    How to handle unseen categories in transform(). If 'error', raises ValueError.
+    If 'use_encoded_value', uses the unknown_value parameter for encoding.
+    The value to use for encoding unknown/unseen categories. Only applicable when
+    handle_unknown='use_encoded_value'. Must be an integer or np.nan.
+    The value to use for encoding missing values (NaN) in the input data.
+    Minimum frequency threshold for a category to be included in the encoding.
+    Categories below this threshold are treated as infrequent.
+    Maximum number of categories to keep per feature.
+Returns
+-------
+    Returns self after fitting (for method chaining).
+Raises
+------
+TypeError
+    If unknown_value is not an integer or np.nan when handle_unknown='use_encoded_value'.
+    If unknown_value is set when handle_unknown is not 'use_encoded_value'.
+ValueError
+    If dtype is not float when encoded_missing_value is np.nan.
+    If unknown_value conflicts with existing category encodings.
+    If input shape doesn't match expected number of features in inverse_transform().
+"""
+             unknown_value=None, encoded_missing_value=np.nan, min_frequency=None,
+             max_categories=None):
+    """Initialize the OrdinalEncoder with specified configuration."""
+"""Fit the OrdinalEncoder to training data and learn category mappings.
+    Parameters
+    ----------
+        The training data to encode. Can contain missing values (NaN).
+        Ignored for OrdinalEncoder as it doesn't use target information.
+    Returns
+    -------
+        Fitted encoder instance with learned category mappings.
+    Raises
+    ------
+    TypeError
+        If unknown_value is not an integer or np.nan when handle_unknown='use_encoded_value'.
+        If unknown_value is set when handle_unknown is not 'use_encoded_value'.
+    ValueError
+        If dtype is not float when encoded_missing_value is np.nan.
+        If unknown_value conflicts with existing category encodings.
+        If missing values exist in features that cannot be encoded with the given dtype.
+    """
+"""Transform input data using the learned category mappings.
+    Parameters
+    ----------
+        The data to encode. Can contain missing values and unknown categories.
+    Returns
+    -------
+        Encoded data with ordinal values for each category. Missing values are
+        replaced with encoded_missing_value, and unknown categories are handled
+        according to handle_unknown setting.
+    Raises
+    ------
+    ValueError
+        If the encoder is not fitted before calling transform().
+        If input shape doesn't match expected number of features.
+    TypeError
+        If X contains invalid data types for encoding.
+    """
+"""Transform encoded data back to original categorical values.
+    Parameters
+    ----------
+        The encoded data to decode. Should contain ordinal values from transform().
+    Returns
+    -------
+        Decoded data with original categorical representations. Missing and unknown
+        categories are marked with special values (None for missing, 'infrequent_sklearn'
+    Raises
+    ------
+    ValueError
+        If the encoder is not fitted before calling inverse_transform().
+        If input shape doesn't match expected number of features.
+        If dtype mismatch between encoded and original data types.
+    Notes
+    -----
+    - Unknown categories are represented as None in the output.
+    - Infrequent categories are marked with 'infrequent_sklearn'.
+    - Missing values (encoded with encoded_missing_value) are also represented as None.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -16288,7 +18224,75 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D pooling layer that reduces the dimensionality of input data using pooling operations.
+This layer performs 1D convolution-like pooling (max, average, etc.) on sequential
+data to reduce spatial dimensions while preserving feature information. It is commonly
+used in temporal sequence processing and time-series analysis applications.
+Attributes:
+Examples:
+    &gt;&gt;&gt; from tensorflow.keras.layers import Pooling1D
+    &gt;&gt;&gt; pool = Pooling1D(pool_size=2, strides=2)
+    &gt;&gt;&gt; # Applies 1D max pooling with window size 2 and stride 2
+"""
+"""Initialize the 1D pooling layer.
+    Args:
+            'max' for max pooling or 'average' for average pooling.
+            For 1D data, this should be an integer representing the window size.
+            Defaults to pool_size if None.
+            (no padding) or 'same' (pad to maintain input shape). Default is 'valid'.
+            determining whether the channel dimension is first or last.
+            be generated based on class and instance parameters.
+    Returns:
+        None (initializes self)
+    Raises:
+            padding, or data_format parameters.
+    Example:
+        &gt;&gt;&gt; pooling_layer = Pooling1D(pool_function='max', pool_size=2, strides=1)
+    """
+    pass
+"""Apply the 1D pooling operation to input data.
+    This method performs the actual pooling computation on the input tensor.
+    It handles dimension expansion and reduction based on the configured
+    data format ('channels_first' or 'channels_last').
+    Args:
+            channels_last format, or (batch_size, features, steps) for
+            channels_first format.
+    Returns:
+            reduced dimensionality along the specified axis. The output
+            shape is computed based on pool_size, strides, and padding.
+    Example:
+        &gt;&gt;&gt; # For input shape (32, 100, 64) with channels_last format
+        &gt;&gt;&gt; output = pooling_layer(inputs)
+        &gt;&gt;&gt; # Output shape would be approximately (32, 50, 64) for pool_size=2
+    """
+    pass
+"""Compute the output shape of the layer given an input shape.
+    This method calculates the expected output tensor dimensions based on
+    the pooling configuration and input shape without performing any computation.
+    Args:
+            the batch dimension. For example, (steps, features) for channels_last
+            or (features, steps) for channels_first format.
+    Returns:
+            after applying the pooling operation. The shape will be
+            (batch_size, length, features) for channels_last or
+            (batch_size, features, length) for channels_first format.
+    Raises:
+    Example:
+        &gt;&gt;&gt; # For input shape (100, 64) with pool_size=2, strides=1
+        &gt;&gt;&gt; output_shape = pooling_layer.compute_output_shape((100, 64))
+        &gt;&gt;&gt; # Returns TensorShape([None, 50, 64]) for channels_last format
+    """
+    pass
+"""Get the configuration dictionary of this layer.
+    This method returns a dictionary containing all parameters used to initialize
+    the layer, which can be used for serialization and deserialization of the
+    model architecture.
+    Returns:
+        dict: A dictionary containing layer configuration with keys:
+            - Plus base Layer configuration (name, dtype, trainable, etc.)
+    Example:
+        &gt;&gt;&gt; config = pooling_layer.get_config()
+        &gt;&gt;&gt; # Returns dict with layer parameters for model serialization</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -16479,7 +18483,31 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>2D Pooling Layer for Neural Networks.
+A pooling layer that applies spatial pooling operations on 4D input tensors to
+downsample feature maps while preserving important features. This layer is commonly
+used in convolutional neural networks for dimensionality reduction and computational
+efficiency.
+Args:
+        callable function that performs the pooling.
+        the pooling window for each dimension.
+        strides for pooling along each dimension. If None, defaults to pool_size.
+        'valid'.
+        whether input channels come first (e.g., NHWC vs NCHW). Defaults to the
+        backend's default image data format.
+        generated based on the class name and parameter values.
+        configuration (e.g., activity_regularizer, kernel_initializer).
+Returns:
+        the input. The output shape depends on padding and stride settings.
+Raises:
+        'channels_last'.
+Examples:
+    &gt;&gt;&gt; pooling = Pooling2D(pool_function='max', pool_size=(2, 2), strides=(2, 2))
+    &gt;&gt;&gt; output = pooling(input_tensor)
+    &gt;&gt;&gt; # Output shape for input (batch, height, width, channels):
+    &gt;&gt;&gt; # (batch, height//2, width//2, channels)
+    &gt;&gt;&gt; pooling_same = Pooling2D(pool_function='average', pool_size=(3, 3),
+    ...                          strides=(1, 1), padding='same')</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -16683,7 +18711,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>3D Pooling Layer for Neural Networks.
+This layer applies 3D pooling operations (max or average) to input tensors with
+5 dimensions (batch, height, width, depth, channels). It supports both
+'channels_first' and 'channels_last' data formats.
+Parameters
+----------
+    The pooling function to use. Common values include 'max', 'average'.
+    This determines the type of pooling operation applied to the input.
+    The size of the pooling window for each dimension (height, width, depth).
+    Must be a 3-tuple specifying the pool size along each spatial dimension.
+    The stride of the pooling operation for each dimension. If None, defaults
+    to pool_size. Must be a 3-tuple matching the number of spatial dimensions.
+    One of 'valid' (no padding) or 'same' (padded to maintain input size).
+    The data format for the input tensor. Either 'channels_first' or
+    'channels_last'. Determines channel dimension position in the tensor.
+    Optional name for the layer, used for identification and debugging.
+    Additional keyword arguments to pass to the parent Layer class.
+Returns
+-------
+    The pooled output tensor with reduced spatial dimensions based on pool_size
+    and strides parameters.
+Raises
+------
+ValueError
+    If pool_size or strides are not 3-tuples, or if padding is not 'valid'/'same'.
+TypeError
+    If data_format is not 'channels_first' or 'channels_last'.
+Examples
+--------
+&gt;&gt;&gt; from tensorflow.keras.layers import Pooling3D
+&gt;&gt;&gt; # Create a max pooling layer with 2x2x2 pool size
+&gt;&gt;&gt; pooling_layer = Pooling3D(pool_function='max', pool_size=(2, 2, 2))
+&gt;&gt;&gt; # Apply to input tensor (batch, height, width, depth, channels)
+&gt;&gt;&gt; output = pooling_layer(input_tensor)
+See Also
+--------</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -17013,7 +19076,30 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Principal Component Analysis (PCA) implementation for dimensionality reduction.
+This class performs Principal Component Analysis using either eigenvalue
+decomposition or Singular Value Decomposition (SVD) to identify the principal
+components that capture maximum variance in the input data. Supports optional
+whitening transformation and provides methods for fitting models and transforming
+new data.
+Attributes:
+        If None, uses all available components (up to min(n_samples, n_features)).
+Parameters:
+        Must be greater than 1 if specified. If None, uses all components.
+        Default is 'svd'. The 'eigen' solver computes covariance matrix first,
+        When True, transforms output to have unit variance along each component.
+Returns:
+        transformed data in principal component space.
+Raises:
+        when specified, or if transform is called on an unfitted model.
+Examples:
+    &gt;&gt;&gt; from sklearn.decomposition import PCA
+    &gt;&gt;&gt; pca = PCA(n_components=2, solver='svd')
+    &gt;&gt;&gt; X_transformed = pca.fit_transform(X)
+    &gt;&gt;&gt; # Using eigen decomposition with whitening
+    &gt;&gt;&gt; pca_eigen = PCA(n_components=3, solver='eigen', whitening=True)
+    &gt;&gt;&gt; X_reduced = pca_eigen.fit_transform(X)
+See Also:</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -17439,7 +19525,18 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>RMSprop optimizer implementation with adaptive learning rates based on squared gradients.
+This optimizer maintains an exponentially decaying average of past squared gradients
+and uses this information to scale the learning rate for each parameter individually.
+It supports optional momentum and centered variants for improved convergence properties.
+Attributes:
+Args:
+Returns:
+Raises:
+Examples:
+    &gt;&gt;&gt; from tensorflow.keras.optimizers import RMSprop
+    &gt;&gt;&gt; optimizer = RMSprop(learning_rate=0.001, rho=0.9, momentum=0.0)
+    &gt;&gt;&gt; optimizer = RMSprop(centered=True, epsilon=1e-5)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -18178,7 +20275,128 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>"""Initialize the SelfTrainingClassifier.
+    Parameters
+    ----------
+        The base estimator to use for self-training. Must have ``fit``,
+        ``predict``, and optionally ``predict_proba`` methods. If None,
+        ``base_estimator`` must be provided (deprecated).
+        Deprecated parameter. Use ``estimator`` instead. Will be removed in
+        version 1.8.
+        Probability threshold for selecting samples when using the 'threshold'
+        criterion. Samples with probability above this value will be selected.
+        Must be between 0.0 and 1.0 (inclusive of 0.0).
+        Criterion for selecting unlabeled samples to label:
+        Number of best samples to select when using the 'k_best' criterion.
+        Must be a positive integer.
+        Maximum number of iterations for self-training. If None, training
+        continues until all samples are labeled.
+        Whether to print progress information during self-training.
+    Returns
+    -------
+    SelfTrainingClassifier
+        The fitted estimator (self).
+    Raises
+    ------
+    ValueError
+        If no estimator is provided and ``base_estimator`` is deprecated, or
+    """
+"""Get the base estimator for predictions.
+    Returns
+    -------
+        The fitted base estimator (cloned from input).
+    Raises
+    ------
+    ValueError
+        If no estimator is provided and ``base_estimator`` is deprecated, or
+    """
+"""Fit the self-training classifier on the dataset.
+    Parameters
+    ----------
+        Target values. Must have numeric dtype. Use -1 for unlabeled samples.
+        String targets must use dtype object.
+        Additional parameters to pass to the underlying estimator's fit method.
+        These are routed to the appropriate methods based on the estimator type.
+    Returns
+    -------
+        The fitted classifier.
+    Raises
+    ------
+    ValueError
+        If ``y`` has string dtype, or if no estimator is provided.
+    Warns
+    -----
+    UserWarning
+        If all samples are labeled (no unlabeled samples to train on).
+    UserWarning
+        If ``k_best`` exceeds the number of unlabeled samples.
+    FutureWarning
+        If using deprecated ``base_estimator`` parameter.
+    """
+"""Predict class labels for samples in X.
+    Parameters
+    ----------
+        Additional parameters to pass to the underlying estimator's predict method.
+    Returns
+    -------
+        Predicted class labels for each sample.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted.
+    """
+"""Predict probability estimates for samples in X.
+    Parameters
+    ----------
+        Additional parameters to pass to the underlying estimator's predict_proba method.
+    Returns
+    -------
+        The probability estimates for each class for each sample.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted.
+    """
+"""Compute decision function scores for samples in X.
+    Parameters
+    ----------
+        Additional parameters to pass to the underlying estimator's decision_function method.
+    Returns
+    -------
+        Decision function scores for each sample.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted, or if the underlying estimator does not
+        support the decision_function method.
+    """
+"""Predict log-probability estimates for samples in X.
+    Parameters
+    ----------
+        Additional parameters to pass to the underlying estimator's predict_log_proba method.
+    Returns
+    -------
+        The log-probability estimates for each class for each sample.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted, or if the underlying estimator does not
+        support the predict_log_proba method.
+    """
+"""Return the mean test set score of the classifier.
+    Parameters
+    ----------
+        True class labels for test samples.
+        Additional parameters to pass to the underlying estimator's score method.
+    Returns
+    -------
+        Mean accuracy on the test set.
+    Raises
+    ------
+    ValueError
+        If the model has not been fitted, or if the underlying estimator does not
+        support the score method.
+    """</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -18437,7 +20655,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Separable Convolution Layer.
+A separable convolution layer that applies depthwise and pointwise convolutions
+separately for computational efficiency. This is commonly used in lightweight
+neural network architectures like MobileNet.
+    Attributes:
+    Raises:
+    Returns:
+    Examples:
+        &gt;&gt;&gt; from tensorflow.keras.layers import SeparableConv
+        &gt;&gt;&gt; conv = SeparableConv(filters=32, kernel_size=3, strides=1)
+        &gt;&gt;&gt; # Use in model building
+        &gt;&gt;&gt; model = tf.keras.Sequential([
+        ...     SeparableConv(filters=32, kernel_size=3),
+        ...     tf.keras.layers.Activation('relu')
+        ... ])
+    Note:
+        This layer implements two separate convolutions:</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -18715,7 +20949,51 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>1D Separable Convolution Layer.
+A 1D separable convolution layer that decomposes the standard convolution into
+depthwise and pointwise convolutions, making it more parameter-efficient by
+reducing the number of learnable parameters compared to a standard convolution.
+This layer is particularly useful for applications where channel independence is
+desired or when computational efficiency is important. It's commonly used in
+mobile and embedded neural network architectures.
+Attributes:
+Parameters:
+        Must be a positive integer.
+        integer or a tuple specifying different sizes per dimension.
+        Default is 1. Can be an integer or tuple of integers.
+        'same' (padding to maintain input size), or 'causal' (for RNN-like
+        applications). Default is 'valid'.
+        Either 'channels_first' (batch_size, channels, width) or
+        'channels_last' (batch_size, width, channels). Default is None.
+        Default is 1.
+        the depthwise convolution layer. Default is 1.
+        the convolution. Can be a string ('relu', 'tanh', etc.) or a callable.
+        Default is None (no activation).
+        Default is True.
+        depthwise convolution kernel weights. Default is 'glorot_uniform'.
+        pointwise convolution kernel weights. Default is 'glorot_uniform'.
+        vector. Default is 'zeros'.
+        depthwise convolution kernel weights. Default is None.
+        pointwise convolution kernel weights. Default is None.
+        vector. Default is None.
+        layer's output. Default is None.
+        the depthwise convolution kernel weights. Default is None.
+        the pointwise convolution kernel weights. Default is None.
+        bias vector. Default is None.
+Returns:
+        operation and optional activation function. Shape depends on input
+        shape, padding, strides, and data_format settings.
+Raises:
+        or if padding is not one of 'valid', 'same', or 'causal'.
+Examples:
+    &gt;&gt;&gt; layer = SeparableConv1D(filters=32, kernel_size=3, strides=1)
+    &gt;&gt;&gt; output = layer(input_tensor)
+    &gt;&gt;&gt; # With activation
+    &gt;&gt;&gt; layer = SeparableConv1D(filters=32, kernel_size=3, activation='relu')
+    &gt;&gt;&gt; output = layer(input_tensor)
+    &gt;&gt;&gt; # With causal padding for RNN-like applications
+    &gt;&gt;&gt; layer = SeparableConv1D(filters=32, kernel_size=3, padding='causal')
+    &gt;&gt;&gt; output = layer(input_tensor)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -18972,7 +21250,36 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Depthwise Separable Convolution Layer for 2D Input.
+This layer implements a depthwise separable convolution operation, commonly used
+in lightweight neural network architectures like MobileNet. It performs two
+channel), followed by a pointwise convolution (1x1 convolution) to combine
+channels.
+Args:
+        of output filters in the convolution). This applies to the pointwise
+        convolution that follows the depthwise operation.
+        width of the 2D convolution window. Can be a single integer to specify
+        the same value for both spatial dimensions.
+        length for the depthwise and pointwise convolutions.
+        the input feature map is only padded where necessary, while "same" pads
+        the input so that the output has the same dimensions as the input.
+        value is None which resolves to the global `image_data_format` setting.
+        rate for the depthwise convolution. Controls the spacing between kernel
+        elements in the input feature map.
+        per input channel. The total number of filters is `filters` * `depth_multiplier`.
+        Can be a string (e.g., "relu", "softmax") or a callable function.
+Returns:
+        output feature map after depthwise and pointwise convolutions, with optional
+        bias addition and activation function application.
+Raises:
+        dilation_rate.
+        configuration.
+Examples:
+    &gt;&gt;&gt; layer = SeparableConv2D(filters=32, kernel_size=(3, 3), strides=1)
+    &gt;&gt;&gt; output = layer(inputs)
+    &gt;&gt;&gt; # Output will have same spatial dimensions as inputs (with padding='same')
+    &gt;&gt;&gt; layer = SeparableConv2D(filters=64, kernel_size=5, padding='valid', activation='relu')
+    &gt;&gt;&gt; output = layer(inputs)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -20254,7 +22561,147 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Sequential Feature Selector using forward/backward selection or floating method.
+This class performs sequential feature selection by iteratively adding or removing
+features based on estimator performance during cross-validation. It supports
+fixed features (always included), feature groups, and various selection strategies.
+Attributes
+----------
+    Base estimator to use for scoring feature subsets. Must be a Classifier or
+    Regressor with an ``_estimator_type`` attribute.
+    Number of features to select. Can be:
+        - An integer specifying exact number of features
+        - A tuple of (min_k, max_k) for range-based selection
+        - 'best' to select the subset with highest average score
+        - 'parsimonious' to select the smallest subset meeting performance criteria
+    If True, performs forward selection (adding features). If False, performs
+    backward elimination (removing features).
+    If True, enables floating method which allows swapping features in/out.
+    Verbosity level for progress output. 0 = silent, 1 = progress bar, &gt;1 = detailed.
+    Scoring metric to evaluate feature subsets. If None, automatically inferred
+    Number of folds for cross-validation or a CV strategy object.
+    Number of jobs to run in parallel. Use -1 for all CPUs.
+    Controls the number of dispatched jobs in parallel processing.
+    Whether to clone the estimator before fitting. If False, uses the same
+    estimator instance for all feature subset evaluations.
+    Features to always include in the selected subset. Can be feature indices
+    (integers) or feature names (strings). If strings are provided, X must be
+    a pandas DataFrame with matching column names.
+    Grouping of features for selection. Each inner list contains feature indices
+    or names that should be selected together. All features in X must be covered
+    by these groups.
+Methods
+-------
+fit(X, y, groups=None, **fit_params)
+    Fit the feature selector on training data.
+Parameters
+----------
+    Training data to fit the feature selector. Can be a pandas DataFrame if
+    feature names are provided in fixed_features or feature_groups.
+    Target values for fitting the estimator.
+    Optional group labels for stratified cross-validation.
+    Additional parameters to pass to the estimator's fit method.
+Returns
+-------
+    Fitted feature selector instance.
+Raises
+------
+TypeError
+    If cv is a generator object instead of an iterable.
+AttributeError
+    If estimator lacks _estimator_type attribute or is neither Classifier nor Regressor.
+ValueError
+    If fixed_features contain invalid types, feature_groups have empty lists,
+    or groups don't cover all features in X.
+transform(X)
+    Transform data using only the selected features.
+Parameters
+----------
+    Data to transform. Can be a pandas DataFrame.
+Returns
+-------
+    Transformed data containing only the selected features.
+Raises
+------
+AttributeError
+    If the selector has not been fitted yet.
+fit_transform(X, y, groups=None, **fit_params)
+    Fit the feature selector and transform data in one step.
+Parameters
+----------
+    Training data.
+    Target values.
+    Optional group labels for stratified cross-validation.
+    Additional parameters for the estimator's fit method.
+Returns
+-------
+    Transformed data with selected features.
+get_metric_dict(confidence_interval=0.95)
+    Get metrics dictionary with confidence intervals for each subset.
+Parameters
+----------
+    Confidence level for interval calculation (e.g., 0.95 for 95%).
+Returns
+-------
+    Dictionary mapping feature count to metric information including:
+Raises
+------
+AttributeError
+    If the selector has not been fitted yet.
+_finalize_fit()
+    Internal method to finalize fitting and select best feature subset.
+_calc_confidence(ary, confidence=0.95)
+    Calculate standard error and confidence bounds for a score array.
+Parameters
+----------
+    Array of scores (e.g., cross-validation scores).
+    Confidence level for interval calculation.
+Returns
+-------
+    Tuple containing (confidence_bound, standard_error).
+Raises
+------
+AttributeError
+    If the selector has not been fitted yet.
+_get_featurenames(subsets, feature_idx, feature_names, n_features)
+    Internal method to get feature names for selected features.
+_check_fitted()
+    Check if the estimator has been fitted.
+Raises
+------
+AttributeError
+    If the selector has not been fitted yet.
+Examples
+--------
+&gt;&gt;&gt; from sklearn.linear_model import LogisticRegression
+&gt;&gt;&gt; from sklearn.datasets import load_breast_cancer
+&gt;&gt;&gt; from SequentialFeatureSelector import SequentialFeatureSelector
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Create feature selector
+&gt;&gt;&gt; sfs = SequentialFeatureSelector(
+...     estimator=LogisticRegression(),
+...     k_features='best',
+...     forward=True,
+...     scoring='accuracy'
+... )
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Load data and fit
+&gt;&gt;&gt; X, y = load_breast_cancer(return_X_y=True)
+&gt;&gt;&gt; sfs.fit(X, y)
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Transform and get selected features
+&gt;&gt;&gt; X_selected = sfs.transform(X)
+&gt;&gt;&gt; print(f"Selected {len(sfs.k_feature_idx_)} features")
+Notes
+-----
+- For string k_features values ('best', 'parsimonious'), the selector will
+  automatically determine the optimal number of features based on scoring.
+- The floating method allows swapping features in/out, which can help find
+  better feature combinations than pure forward or backward selection.
+- Use fixed_features to ensure certain features are always included in the
+  selected subset (e.g., important clinical markers).
+- Feature groups allow selecting features that should be treated together
+  (e.g., gene expression from the same pathway).</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -20531,7 +22978,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Stochastic Gradient Descent optimizer with optional momentum and Nesterov acceleration.
+This optimizer implements the standard SGD algorithm with support for momentum-based
+weight updates and optional Nesterov accelerated gradient (NAG). It extends the
+OptimizerV2 base class and supports both dense and sparse gradient applications.
+Attributes:
+Args:
+        This controls the step size for each parameter update.
+        between 0 and 1 if provided as a numeric value. Can also be a tensor or
+        callable function for dynamic momentum scheduling.
+        which looks ahead to the future position before updating parameters.
+        and debugging purposes.
+Raises:
+Returns:
+Examples:
+    &gt;&gt;&gt; # Basic SGD optimizer
+    &gt;&gt;&gt; optimizer = SGD(learning_rate=0.01)
+    &gt;&gt;&gt; # SGD with momentum
+    &gt;&gt;&gt; optimizer = SGD(learning_rate=0.01, momentum=0.9)
+    &gt;&gt;&gt; # Nesterov accelerated SGD
+    &gt;&gt;&gt; optimizer = SGD(learning_rate=0.01, momentum=0.9, nesterov=True)
+    &gt;&gt;&gt; # Dynamic momentum with tensor
+    &gt;&gt;&gt; momentum_tensor = tf.constant(0.9)
+    &gt;&gt;&gt; optimizer = SGD(learning_rate=0.01, momentum=momentum_tensor)
+Notes:
+    - When momentum is enabled, additional state variables are created to store
+      momentum values for each trainable variable.
+    - The optimizer supports distributed training through resource-based operations.
+    - For sparse gradients, the optimizer handles both regular and duplicate indices.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -20855,7 +23329,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Softmax Regression Multi-Class Classifier.
+A multi-class classifier that uses softmax regression (multinomial logistic
+regression) to predict class probabilities. The model applies gradient descent
+optimization with optional L2 regularization and supports minibatch training.
+Attributes:
+        Learning rate for gradient descent optimization. Default is 0.01.
+        Number of training iterations/epochs. Default is 50.
+        L2 regularization coefficient. Set to 0 for no regularization. Default is 0.0.
+        Number of minibatches per epoch. Value of 1 means full batch gradient descent. Default is 1.
+        Number of output classes. If None, automatically detected from target data. Default is None.
+        Random seed for reproducibility of weight initialization and shuffling. Default is None.
+        Whether to print training progress during fitting. Default is 0 (False).
+Methods:
+    predict_proba(X) -&gt; ndarray
+        Return probability estimates for each class.
+    _predict(X) -&gt; ndarray
+        Return predicted class labels based on probability scores.
+    _fit(X, y, init_params=True) -&gt; self
+        Fit the model using gradient descent with optional L2 regularization and minibatch training.
+Notes:
+    - The model is stateful; predict methods require prior fitting via _fit().
+    - Softmax activation ensures output probabilities sum to 1 across classes.
+    - Cross-entropy loss is used for optimization with optional L2 regularization term.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -21568,7 +24064,57 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>TargetEncoder encodes categorical features using target statistics.
+This encoder represents each category of a categorical feature by the mean
+of the target variable for that category, computed via cross-validation to
+prevent data leakage. It supports binary, continuous, and multiclass targets.
+The encoding process uses K-Fold or StratifiedK-Fold cross-validation to fit
+encodings on training folds while evaluating on held-out folds, ensuring
+that encodings are not influenced by the target values of test samples.
+Parameters
+----------
+    How to handle categories. If 'auto', uses observed categories from training data.
+    If a list, specifies how many categories per feature.
+    Type of target encoding to use. 'auto' infers the type from y. For multiclass,
+    each category is encoded with a separate mean per class.
+    Smoothing parameter for target mean calculation. If 'auto', uses variance-based
+    smoothing. Otherwise, applies specified smoothing value to reduce overfitting.
+    Number of cross-validation folds. Must be &gt;= 2.
+    Whether to shuffle data during CV splits. Only used when target_type is 'continuous'.
+    Random seed for reproducibility. Used in cross-validation splits.
+Attributes
+----------
+    The categories observed for each feature after fitting.
+    The unique classes found in the target variable (for multiclass encoding).
+    The fitted encodings mapping categories to encoded values.
+    The mean target value for each category, used for unknown categories.
+    Number of features seen during fit.
+    Total number of categories across all features.
+    Inferred or set target type ('binary', 'continuous', 'multiclass').
+See Also
+--------
+Examples
+--------
+&gt;&gt;&gt; from sklearn.preprocessing import TargetEncoder
+&gt;&gt;&gt; from sklearn.datasets import make_classification
+&gt;&gt;&gt; X, y = make_classification(n_samples=1000, n_features=4, random_state=42)
+&gt;&gt;&gt; enc = TargetEncoder(random_state=42)
+&gt;&gt;&gt; enc.fit(X, y)
+&gt;&gt;&gt; X_encoded = enc.transform(X)
+For multiclass targets:
+&gt;&gt;&gt; from sklearn.preprocessing import TargetEncoder
+&gt;&gt;&gt; import numpy as np
+&gt;&gt;&gt; X = np.array([['A'], ['B'], ['C']])
+&gt;&gt;&gt; y = np.array([0, 1, 2])
+&gt;&gt;&gt; enc = TargetEncoder(target_type='multiclass', random_state=42)
+&gt;&gt;&gt; enc.fit(X, y)
+&gt;&gt;&gt; enc.transform(X)
+Notes
+-----
+- Unknown categories (not seen during fit) are encoded with the target mean.
+- The encoder requires a target variable y during fit.
+- For multiclass targets, each class gets its own encoding column.
+- Use smooth parameter to control overfitting on training data.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -21843,7 +24389,78 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Transformer for encoding transaction data into binary matrix representation.
+This encoder converts market basket transactions (collections of items) into 
+binary matrix formats suitable for machine learning algorithms. Each unique 
+item becomes a feature column, and each row represents a transaction where 
+items are marked as True/1 if present in that transaction.
+Attributes:
+Methods:
+"""
+"""Initialize the TransactionEncoder with no parameters.
+    Returns:
+        None
+    """
+"""Learn the set of unique items and create column mappings.
+    Args:
+            (list or set) of item names/identifiers
+    Returns:
+    Attributes Set:
+    """
+    unique_items = set()
+            unique_items.add(item)
+    columns_mapping = {}
+        columns_mapping[item] = col_idx
+"""Transform transactions into binary matrix representation.
+    Args:
+            (list or set) of item names/identifiers
+    Returns:
+        Encoded binary matrix where rows are transactions and columns 
+        are unique items. Values are True if item exists in transaction, 
+        False otherwise.
+    Raises:
+    Note:
+        The encoder must be fitted before calling transform.
+    """
+        indptr = [0]
+        indices = []
+                col_idx = self.columns_mapping_[item]
+                indices.append(col_idx)
+            indptr.append(len(indices))
+        non_sparse_values = [True] * len(indices)
+        array = csr_matrix((non_sparse_values, indices, indptr), dtype=bool)
+    else:
+        array = np.zeros((len(X), len(self.columns_)), dtype=bool)
+                col_idx = self.columns_mapping_[item]
+                array[row_idx, col_idx] = True
+"""Convert binary matrix back to list of transactions.
+    Args:
+            rows are transactions and columns are unique items from 
+            training data
+    Returns:
+        List of transactions where each transaction is a list of 
+        item names present in that row
+    Raises:
+    Note:
+        The encoder must be fitted before calling inverse_transform.
+        Only columns corresponding to True values will appear in output.
+    """
+"""Fit the encoder and transform data in one call.
+    Args:
+            (list or set) of item names/identifiers
+    Returns:
+        Encoded binary matrix after fitting and transforming
+    Note:
+        Convenience method that combines fit() and transform() operations.
+        Useful when you only need the transformed output.
+    """
+"""Get feature names (item names) after fitting.
+    Returns:
+        List of sorted unique item names from training data
+    Raises:
+    Note:
+        This method is useful for inspecting what features were learned 
+        during the fit() operation.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -21976,7 +24593,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>UpSampling1D layer that upsamples 1D data by repeating elements along axis 1.
+This layer performs upsampling on 3D tensors (batch, sequence, features) by
+repeating elements along the sequence dimension (axis=1). It is commonly used
+in time-series models, audio processing, and other applications requiring
+temporal resolution increases.
+Example usage:
+    &gt;&gt;&gt; upsample = UpSampling1D(size=2)  # Doubles sequence length
+    &gt;&gt;&gt; x = upsample(x)  # Each element repeated twice along axis 1
+Args:
+        along axis 1 will be repeated this many times. Default is 2.
+Returns:
+        multiplied by size, while batch and feature dimensions remain unchanged.
+Raises:</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22178,7 +24807,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Upsample 4D input images by the specified height and width factors.
+This layer upsamples input images (batch, channels, height, width) by the 
+specified size factors in each dimension. The data format can be either 
+'channels_first' or 'channels_last'.
+Examples:
+    &gt;&gt;&gt; # Upsample by factor of 2x
+    &gt;&gt;&gt; upsample = UpSampling2D(size=(2, 2))
+    &gt;&gt;&gt; output = upsample(input_tensor)
+Args:
+        and width. Default is (2, 2). If a dimension is None, that dimension 
+        will not be scaled.
+        'channels_first' or 'channels_last'. Default is None which inherits from 
+        global configuration.
+        Must be one of 'nearest' or 'bilinear'. Default is 'nearest'.
+Returns:
+        (or [batch, height, width, channels] depending on data_format).
+Raises:
+See Also:
+Note:
+    This layer is commonly used in U-Net architectures and other models requiring 
+    spatial upscaling during the decoder path. The interpolation method affects 
+    image quality - 'bilinear' produces smoother results while 'nearest' preserves 
+    sharp edges but may introduce aliasing artifacts.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -22349,7 +25000,36 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>"""Initialize a 3D upsampling layer.
+        Args:
+                dimension (depth, height, width). Default is (2, 2, 2). Each value
+                represents how much to increase that dimension.
+                determines the order of dimensions in tensors. If None, uses the
+                default from Keras configuration.
+        Returns:
+            None (initializes instance attributes).
+        Raises:
+                data_format is not "channels_first" or "channels_last".
+        """
+        """Compute the output shape after upsampling.
+        Args:
+                should have 5 dimensions for 3D data (batch, channels or depth,
+                height, width). Some dimensions can be None if unknown.
+        Returns:
+                upsampling. Spatial dimensions are multiplied by their respective
+                size factors. Channel dimension is preserved unchanged.
+        Raises:
+                invalid values.
+        """
+        """Apply the upsampling operation to the input tensor.
+        Args:
+                width) for channels_last format. All spatial dimensions must be
+                integers.
+        Returns:
+                spatial dimension according to the size parameter. The returned
+                tensor has the same data format as the input.
+        Raises:
+        """</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -22503,7 +25183,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>A layer that adds zero padding to 1D sequences (temporal dimension).
+This layer pads the sequence dimension of 3D input tensors with zeros at
+the beginning and/or end, useful for handling variable-length sequences or
+aligning inputs before processing.
+Attributes
+----------
+    The amount of padding to add. Can be a single integer (same padding on
+    both sides) or a tuple of (left_padding, right_padding). Default is 1.
+    Specifies the expected input dimensionality (3D tensor with shape
+    [batch_size, sequence_length, features]).
+Methods
+-------
+compute_output_shape(input_shape) -&gt; TensorShape
+    Computes the output shape based on input shape and padding values.
+    Parameters
+    ----------
+        Shape of input tensor as a list/tuple of integers (None allowed).
+    Returns
+    -------
+    TensorShape
+        Output shape with padded sequence length. If input sequence length
+        is None, output sequence length remains None.
+call(inputs) -&gt; Tensor
+    Applies zero padding to the input tensor along the sequence dimension.
+    Parameters
+    ----------
+        Input tensor of shape (batch_size, sequence_length, features).
+    Returns
+    -------
+    Tensor
+        Padded input tensor with same dtype and batch/features dimensions.
+get_config() -&gt; dict
+    Returns a dictionary containing configuration for the layer.
+    Returns
+    -------
+    dict
+        Dictionary with 'padding' key containing the normalized padding value.
+Examples
+--------
+&gt;&gt;&gt; # Create ZeroPadding1D layer with 2 units of padding on each side
+&gt;&gt;&gt; padding = ZeroPadding1D(padding=2)
+&gt;&gt;&gt; 
+&gt;&gt;&gt; # Apply to a tensor of shape (32, 10, 64)
+&gt;&gt;&gt; padded_output = padding(x)
+See Also
+--------</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -22777,7 +25502,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>A layer that adds zero-padding to the top, bottom, left, and right of 4D input tensors.
+This layer pads the input tensor by adding zeros along the height and width dimensions.
+It supports both 'channels_first' and 'channels_last' data formats for flexibility
+in different model architectures.
+Examples:
+    # Symmetric padding (same amount on all sides)
+    &gt;&gt;&gt; layer = ZeroPadding2D(padding=1)
+    # Different padding for height and width
+    &gt;&gt;&gt; layer = ZeroPadding2D(padding=(1, 2))
+    # Asymmetric padding (different top/bottom or left/right)
+    &gt;&gt;&gt; layer = ZeroPadding2D(padding=((1, 2), (3, 4)))
+Args:
+    padding: Padding configuration. Can be:
+        Determines whether the input tensor has shape (batch, channels, height, width)
+        or (batch, height, width, channels). Defaults to None which infers from model.
+Returns:
+        that were not specified in the input shape.
+Raises:
+See Also:</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -23054,7 +25797,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>3D Zero Padding Layer.
+This layer pads 3D tensors with zeros, typically used before or after convolutional layers
+to adjust tensor dimensions. It supports both symmetric and asymmetric padding across all
+three spatial dimensions (depth, height, width).
+Args:
+    padding: Padding configuration for the three spatial dimensions. Can be:
+        Default is (1, 1, 1).
+        in which the channels dimension appears in the input tensor. Defaults to None
+        (will be normalized based on backend defaults).
+Returns:
+Raises:
+                Also raised if padding tuple has length other than 3.
+Examples:
+    &gt;&gt;&gt; # Symmetric padding of 1 to all dimensions
+    &gt;&gt;&gt; layer = ZeroPadding3D(padding=1)
+    &gt;&gt;&gt; 
+    &gt;&gt;&gt; # Asymmetric padding (different left/right for each dimension)
+    &gt;&gt;&gt; layer = ZeroPadding3D(padding=((0, 2), (1, 1), (1, 1)))
+    &gt;&gt;&gt; 
+    &gt;&gt;&gt; # Channels-first format with asymmetric padding
+    &gt;&gt;&gt; layer = ZeroPadding3D(padding=(0, 2), data_format='channels_first')
+Note:
+    The input tensor should have shape (batch_size, channels, depth, height, width) for
+    channels_first or (batch_size, depth, height, width, channels) for channels_last.
+    The layer adds zeros around the spatial dimensions without modifying the batch or
+    channel dimensions.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -23713,7 +26481,102 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t># ERROR: CoT Docstring generation failed.</t>
+          <t>Base encoder class for categorical feature encoding with infrequent category support.
+This class provides functionality to encode categorical features into numerical representations
+TransformerMixin and BaseEstimator from scikit-learn.
+Methods:
+"""
+"""Validate and prepare input array X for categorical encoding.
+    Checks if X is a valid 2D array-like object with iloc attribute. If not,
+    converts using check_array with appropriate dtype settings. Handles string
+    dtypes specially by converting to object dtype when necessary.
+    Args:
+            Can be pandas DataFrame, numpy array, or other 2D array-like object.
+            Whether to check if all values are finite. If False, allows NaN/Inf.
+    Returns:
+        tuple: (X_columns, n_samples, n_features) where:
+    Raises:
+    """
+"""Fit the categorical encoder on training data.
+    Processes each categorical column to extract unique categories and validate
+    against user-provided or auto-detected category lists. Handles unknown
+    categories according to handle_unknown parameter and optionally computes
+    category frequency counts.
+    Args:
+            categorical features to encode. Can be pandas DataFrame or numpy array.
+            How to handle unseen categories during transform. 'error' raises ValueError,
+            'ignore' masks unknown values, 'infrequent_if_exist' maps to infrequent category.
+            Whether to check if all values are finite. If False, allows NaN/Inf.
+            Whether to return category frequency counts in output dictionary.
+            Whether to return indices of missing categories for infrequent handling.
+    Returns:
+        dict: Dictionary containing:
+                return_counts is True or infrequent handling is enabled
+                return_and_ignore_missing_for_infrequent is True
+    Raises:
+            categories detected, unsorted numerical categories, or NaN not at end
+            of user-provided categories. Also raised for unknown categories when
+            handle_unknown='error' during fit.
+    """
+"""Transform new data using fitted encoder.
+    Applies the fitted category mappings to encode categorical features into
+    numerical representations. Checks for unknown categories and handles them
+    according to handle_unknown setting. Warns about unknown categories if enabled.
+    Args:
+            categorical features to encode. Must have same number of features
+            as training data.
+            How to handle unseen categories during transform. 'error' raises ValueError,
+            'ignore' masks unknown values, 'infrequent_if_exist' maps to infrequent category.
+            Whether to check if all values are finite. If False, allows NaN/Inf.
+            Whether to emit warnings when unknown categories are found.
+            Dictionary mapping feature indices to category values to ignore during encoding.
+    Returns:
+        tuple: (X_int, X_mask) where:
+    Raises:
+            number of features doesn't match training data.
+    """
+@property
+"""Return infrequent category indices for each feature column.
+    Accesses the stored infrequent category indices from the fitted encoder.
+    Returns None for columns without infrequent categories.
+    Returns:
+            categories for the corresponding feature column. Contains None
+    """
+"""Check if infrequent category handling is enabled.
+    Determines whether infrequent category detection and mapping should be performed
+    based on max_categories and min_frequency configuration parameters.
+    Returns:
+    """
+"""Identify categories below frequency thresholds as infrequent.
+    Determines which categories should be treated as infrequent based on their
+    occurrence count relative to min_frequency threshold and max_categories limit.
+    Args:
+            frequency counts for each category in the column.
+    Returns:
+            categories are identified as infrequent.
+    """
+"""Build mapping array separating frequent and infrequent categories.
+    Creates a mapping where infrequent categories are mapped to a single value
+    (n_frequent_cats) and frequent categories get sequential values from 0 to
+    n_frequent_cats - 1. Handles missing indices for columns with NaN categories.
+    Args:
+            or empty dict if no missing categories exist.
+    Returns:
+            internally.
+    """
+"""Apply infrequent category mappings to encoded data.
+    Maps infrequent categories to their designated values in the encoded array.
+    Handles unknown categories when handle_unknown='infrequent_if_exist'. Respects
+            ignore_category_indices for specific feature columns.
+    Args:
+            to exclude from infrequent category mapping.
+    Returns:
+    """
+"""Return estimator metadata about supported input types and configurations.
+    Provides information about the expected input array types and whether NaN
+    values are allowed during fitting and transformation.
+    Returns:
+        dict: Metadata dictionary containing:</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
